--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2715" uniqueCount="436">
   <si>
     <t>ClubHub Insight</t>
   </si>
@@ -80,13 +80,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>01/09/2026, 12:28:20</t>
+    <t>01/09/2026, 16:12:07</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>9m 33s</t>
+    <t>8m 58s</t>
   </si>
   <si>
     <t>Version</t>
@@ -137,7 +137,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5638 ms</t>
+    <t>5299 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">    ├── 📁 Recreational Gymnastics Judging Resource – British Gymnastics Club Hub Resources (1)</t>
   </si>
   <si>
-    <t xml:space="preserve">    │   └── 📄 Recreational Gymnastics Judging resource – British Gymnastics Club Hub Resources</t>
+    <t xml:space="preserve">    │   └── 📄 (Failed)</t>
   </si>
   <si>
     <t xml:space="preserve">    ├── 📄 Financial Toolkit – British Gymnastics Club Hub Resources</t>
@@ -1176,9 +1176,6 @@
   </si>
   <si>
     <t>https://clubhub-resources.british-gymnastics.org/courses/toolkits/lessons/health-and-safety-toolkit/topic/health-and-safety-management-overview</t>
-  </si>
-  <si>
-    <t>Recreational Gymnastics Judging resource – British Gymnastics Club Hub Resources</t>
   </si>
   <si>
     <t>https://clubhub-resources.british-gymnastics.org/courses/toolkits/lessons/recreational-gymnastics-judging-toolkit/topic/recreational-gymnastics-judging-resource</t>
@@ -2018,10 +2015,10 @@
         <v>152</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2041,7 +2038,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2061,7 +2058,7 @@
         <v>25</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,7 +2078,7 @@
         <v>29</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,7 +2098,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2121,7 +2118,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2141,7 +2138,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2161,7 +2158,7 @@
         <v>25</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2181,7 +2178,7 @@
         <v>31</v>
       </c>
       <c r="F9" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2201,7 +2198,7 @@
         <v>29</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2221,7 +2218,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2241,7 +2238,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2261,7 +2258,7 @@
         <v>25</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2281,7 +2278,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2301,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2321,7 +2318,7 @@
         <v>34</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2341,7 +2338,7 @@
         <v>29</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2361,7 +2358,7 @@
         <v>25</v>
       </c>
       <c r="F18" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2381,7 +2378,7 @@
         <v>35</v>
       </c>
       <c r="F19" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2401,7 +2398,7 @@
         <v>29</v>
       </c>
       <c r="F20" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2421,7 +2418,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2441,7 +2438,7 @@
         <v>27</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2461,7 +2458,7 @@
         <v>29</v>
       </c>
       <c r="F23" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2481,7 +2478,7 @@
         <v>25</v>
       </c>
       <c r="F24" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2501,7 +2498,7 @@
         <v>35</v>
       </c>
       <c r="F25" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2521,7 +2518,7 @@
         <v>35</v>
       </c>
       <c r="F26" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2541,7 +2538,7 @@
         <v>29</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2561,7 +2558,7 @@
         <v>25</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2581,7 +2578,7 @@
         <v>25</v>
       </c>
       <c r="F29" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2601,7 +2598,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2621,7 +2618,7 @@
         <v>31</v>
       </c>
       <c r="F31" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2641,7 +2638,7 @@
         <v>25</v>
       </c>
       <c r="F32" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2661,7 +2658,7 @@
         <v>41</v>
       </c>
       <c r="F33" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2681,7 +2678,7 @@
         <v>40</v>
       </c>
       <c r="F34" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2701,7 +2698,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2721,7 +2718,7 @@
         <v>25</v>
       </c>
       <c r="F36" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2741,7 +2738,7 @@
         <v>40</v>
       </c>
       <c r="F37" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2761,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2781,7 +2778,7 @@
         <v>38</v>
       </c>
       <c r="F39" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2801,7 +2798,7 @@
         <v>25</v>
       </c>
       <c r="F40" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2821,7 +2818,7 @@
         <v>33</v>
       </c>
       <c r="F41" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2841,7 +2838,7 @@
         <v>33</v>
       </c>
       <c r="F42" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2861,7 +2858,7 @@
         <v>32</v>
       </c>
       <c r="F43" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2881,7 +2878,7 @@
         <v>33</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2901,7 +2898,7 @@
         <v>35</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2921,7 +2918,7 @@
         <v>31</v>
       </c>
       <c r="F46" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2941,7 +2938,7 @@
         <v>25</v>
       </c>
       <c r="F47" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,7 +2958,7 @@
         <v>25</v>
       </c>
       <c r="F48" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2981,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="F49" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3001,7 +2998,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3021,7 +3018,7 @@
         <v>44</v>
       </c>
       <c r="F51" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3041,7 +3038,7 @@
         <v>30</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3061,7 +3058,7 @@
         <v>28</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3081,7 +3078,7 @@
         <v>29</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3101,7 +3098,7 @@
         <v>34</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3121,7 +3118,7 @@
         <v>28</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3141,7 +3138,7 @@
         <v>48</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3161,7 +3158,7 @@
         <v>28</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3181,7 +3178,7 @@
         <v>38</v>
       </c>
       <c r="F59" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3201,7 +3198,7 @@
         <v>25</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,7 +3218,7 @@
         <v>25</v>
       </c>
       <c r="F61" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,7 +3238,7 @@
         <v>29</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3261,7 +3258,7 @@
         <v>25</v>
       </c>
       <c r="F63" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3281,7 +3278,7 @@
         <v>25</v>
       </c>
       <c r="F64" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3301,7 +3298,7 @@
         <v>42</v>
       </c>
       <c r="F65" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3321,7 +3318,7 @@
         <v>28</v>
       </c>
       <c r="F66" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,7 +3338,7 @@
         <v>25</v>
       </c>
       <c r="F67" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3361,7 +3358,7 @@
         <v>30</v>
       </c>
       <c r="F68" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,7 +3378,7 @@
         <v>28</v>
       </c>
       <c r="F69" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,7 +3398,7 @@
         <v>26</v>
       </c>
       <c r="F70" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3421,7 +3418,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,7 +3438,7 @@
         <v>25</v>
       </c>
       <c r="F72" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,7 +3458,7 @@
         <v>26</v>
       </c>
       <c r="F73" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,7 +3478,7 @@
         <v>28</v>
       </c>
       <c r="F74" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3501,7 +3498,7 @@
         <v>30</v>
       </c>
       <c r="F75" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3521,7 +3518,7 @@
         <v>28</v>
       </c>
       <c r="F76" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3541,7 +3538,7 @@
         <v>28</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,7 +3558,7 @@
         <v>26</v>
       </c>
       <c r="F78" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,7 +3578,7 @@
         <v>28</v>
       </c>
       <c r="F79" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3601,35 +3598,35 @@
         <v>26</v>
       </c>
       <c r="F80" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B81" t="s">
         <v>384</v>
       </c>
-      <c r="B81" t="s">
-        <v>385</v>
-      </c>
       <c r="C81">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E81">
-        <v>33</v>
-      </c>
-      <c r="F81" s="35" t="s">
-        <v>434</v>
+        <v>0</v>
+      </c>
+      <c r="F81" s="36" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>385</v>
+      </c>
+      <c r="B82" t="s">
         <v>386</v>
-      </c>
-      <c r="B82" t="s">
-        <v>387</v>
       </c>
       <c r="C82">
         <v>40</v>
@@ -3641,15 +3638,15 @@
         <v>40</v>
       </c>
       <c r="F82" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>387</v>
+      </c>
+      <c r="B83" t="s">
         <v>388</v>
-      </c>
-      <c r="B83" t="s">
-        <v>389</v>
       </c>
       <c r="C83">
         <v>29</v>
@@ -3661,15 +3658,15 @@
         <v>29</v>
       </c>
       <c r="F83" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>389</v>
+      </c>
+      <c r="B84" t="s">
         <v>390</v>
-      </c>
-      <c r="B84" t="s">
-        <v>391</v>
       </c>
       <c r="C84">
         <v>34</v>
@@ -3681,16 +3678,16 @@
         <v>35</v>
       </c>
       <c r="F84" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>391</v>
+      </c>
+      <c r="B85" t="s">
         <v>392</v>
       </c>
-      <c r="B85" t="s">
-        <v>393</v>
-      </c>
       <c r="C85">
         <v>0</v>
       </c>
@@ -3701,15 +3698,15 @@
         <v>0</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>394</v>
+      </c>
+      <c r="B86" t="s">
         <v>395</v>
-      </c>
-      <c r="B86" t="s">
-        <v>396</v>
       </c>
       <c r="C86">
         <v>38</v>
@@ -3721,15 +3718,15 @@
         <v>39</v>
       </c>
       <c r="F86" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>396</v>
+      </c>
+      <c r="B87" t="s">
         <v>397</v>
-      </c>
-      <c r="B87" t="s">
-        <v>398</v>
       </c>
       <c r="C87">
         <v>40</v>
@@ -3741,15 +3738,15 @@
         <v>40</v>
       </c>
       <c r="F87" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>398</v>
+      </c>
+      <c r="B88" t="s">
         <v>399</v>
-      </c>
-      <c r="B88" t="s">
-        <v>400</v>
       </c>
       <c r="C88">
         <v>28</v>
@@ -3761,15 +3758,15 @@
         <v>28</v>
       </c>
       <c r="F88" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>400</v>
+      </c>
+      <c r="B89" t="s">
         <v>401</v>
-      </c>
-      <c r="B89" t="s">
-        <v>402</v>
       </c>
       <c r="C89">
         <v>23</v>
@@ -3781,15 +3778,15 @@
         <v>23</v>
       </c>
       <c r="F89" s="32" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>402</v>
+      </c>
+      <c r="B90" t="s">
         <v>403</v>
-      </c>
-      <c r="B90" t="s">
-        <v>404</v>
       </c>
       <c r="C90">
         <v>26</v>
@@ -3801,15 +3798,15 @@
         <v>26</v>
       </c>
       <c r="F90" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>404</v>
+      </c>
+      <c r="B91" t="s">
         <v>405</v>
-      </c>
-      <c r="B91" t="s">
-        <v>406</v>
       </c>
       <c r="C91">
         <v>28</v>
@@ -3821,7 +3818,7 @@
         <v>29</v>
       </c>
       <c r="F91" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3829,7 +3826,7 @@
         <v>224</v>
       </c>
       <c r="B92" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C92">
         <v>25</v>
@@ -3841,7 +3838,7 @@
         <v>25</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3849,7 +3846,7 @@
         <v>204</v>
       </c>
       <c r="B93" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C93">
         <v>25</v>
@@ -3861,15 +3858,15 @@
         <v>25</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>408</v>
+      </c>
+      <c r="B94" t="s">
         <v>409</v>
-      </c>
-      <c r="B94" t="s">
-        <v>410</v>
       </c>
       <c r="C94">
         <v>25</v>
@@ -3881,15 +3878,15 @@
         <v>25</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>410</v>
+      </c>
+      <c r="B95" t="s">
         <v>411</v>
-      </c>
-      <c r="B95" t="s">
-        <v>412</v>
       </c>
       <c r="C95">
         <v>25</v>
@@ -3901,15 +3898,15 @@
         <v>25</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>412</v>
+      </c>
+      <c r="B96" t="s">
         <v>413</v>
-      </c>
-      <c r="B96" t="s">
-        <v>414</v>
       </c>
       <c r="C96">
         <v>25</v>
@@ -3921,15 +3918,15 @@
         <v>25</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>414</v>
+      </c>
+      <c r="B97" t="s">
         <v>415</v>
-      </c>
-      <c r="B97" t="s">
-        <v>416</v>
       </c>
       <c r="C97">
         <v>36</v>
@@ -3941,15 +3938,15 @@
         <v>37</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>416</v>
+      </c>
+      <c r="B98" t="s">
         <v>417</v>
-      </c>
-      <c r="B98" t="s">
-        <v>418</v>
       </c>
       <c r="C98">
         <v>35</v>
@@ -3961,15 +3958,15 @@
         <v>35</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>418</v>
+      </c>
+      <c r="B99" t="s">
         <v>419</v>
-      </c>
-      <c r="B99" t="s">
-        <v>420</v>
       </c>
       <c r="C99">
         <v>28</v>
@@ -3981,15 +3978,15 @@
         <v>28</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" t="s">
         <v>421</v>
-      </c>
-      <c r="B100" t="s">
-        <v>422</v>
       </c>
       <c r="C100">
         <v>28</v>
@@ -4001,16 +3998,16 @@
         <v>28</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>422</v>
+      </c>
+      <c r="B101" t="s">
         <v>423</v>
       </c>
-      <c r="B101" t="s">
-        <v>424</v>
-      </c>
       <c r="C101">
         <v>0</v>
       </c>
@@ -4021,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4126,7 +4123,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="12">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4134,7 +4131,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4174,7 +4171,7 @@
         <v>28</v>
       </c>
       <c r="B19" s="12">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4179,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="14">
-        <v>2794</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4190,7 +4187,7 @@
         <v>30</v>
       </c>
       <c r="B21" s="12">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4238,7 +4235,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="12">
-        <v>5910</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4243,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="14">
-        <v>1439</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4928,7 +4925,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" s="20">
         <v>59</v>
@@ -4955,7 +4952,7 @@
         <v>171</v>
       </c>
       <c r="T2" s="22">
-        <v>4099</v>
+        <v>4161</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>172</v>
@@ -4999,7 +4996,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="20">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L3" s="20">
         <v>48</v>
@@ -5026,7 +5023,7 @@
         <v>180</v>
       </c>
       <c r="T3" s="22">
-        <v>5709</v>
+        <v>4504</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>172</v>
@@ -5070,7 +5067,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L4" s="20">
         <v>75</v>
@@ -5097,7 +5094,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5297</v>
+        <v>5194</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>185</v>
@@ -5141,7 +5138,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L5" s="20">
         <v>66</v>
@@ -5168,7 +5165,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5309</v>
+        <v>5323</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>185</v>
@@ -5212,7 +5209,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L6" s="20">
         <v>61</v>
@@ -5239,7 +5236,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5150</v>
+        <v>5186</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>185</v>
@@ -5283,7 +5280,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L7" s="20">
         <v>58</v>
@@ -5310,7 +5307,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4878</v>
+        <v>4417</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>185</v>
@@ -5354,7 +5351,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L8" s="20">
         <v>62</v>
@@ -5381,7 +5378,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4403</v>
+        <v>4650</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>185</v>
@@ -5425,7 +5422,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="20">
         <v>56</v>
@@ -5452,7 +5449,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4707</v>
+        <v>4575</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>185</v>
@@ -5496,7 +5493,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="20">
         <v>55</v>
@@ -5523,7 +5520,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4242</v>
+        <v>4694</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>185</v>
@@ -5567,7 +5564,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11" s="20">
         <v>56</v>
@@ -5594,7 +5591,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>4597</v>
+        <v>6199</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>185</v>
@@ -5638,7 +5635,7 @@
         <v>13</v>
       </c>
       <c r="K12" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L12" s="20">
         <v>70</v>
@@ -5665,7 +5662,7 @@
         <v>210</v>
       </c>
       <c r="T12" s="22">
-        <v>4588</v>
+        <v>4138</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>172</v>
@@ -5709,7 +5706,7 @@
         <v>13</v>
       </c>
       <c r="K13" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L13" s="20">
         <v>60</v>
@@ -5736,7 +5733,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>3951</v>
+        <v>4260</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>185</v>
@@ -5780,7 +5777,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L14" s="20">
         <v>56</v>
@@ -5807,7 +5804,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>5090</v>
+        <v>4594</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>185</v>
@@ -5851,7 +5848,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L15" s="20">
         <v>85</v>
@@ -5878,7 +5875,7 @@
         <v>218</v>
       </c>
       <c r="T15" s="22">
-        <v>5961</v>
+        <v>4974</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>172</v>
@@ -5922,7 +5919,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L16" s="20">
         <v>59</v>
@@ -5949,7 +5946,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>7698</v>
+        <v>4941</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>185</v>
@@ -5993,7 +5990,7 @@
         <v>13</v>
       </c>
       <c r="K17" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L17" s="20">
         <v>57</v>
@@ -6020,7 +6017,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>5395</v>
+        <v>5026</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>185</v>
@@ -6064,7 +6061,7 @@
         <v>13</v>
       </c>
       <c r="K18" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L18" s="20">
         <v>82</v>
@@ -6091,7 +6088,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>6077</v>
+        <v>5409</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>185</v>
@@ -6135,7 +6132,7 @@
         <v>13</v>
       </c>
       <c r="K19" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L19" s="20">
         <v>63</v>
@@ -6162,7 +6159,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>4904</v>
+        <v>4637</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>185</v>
@@ -6206,7 +6203,7 @@
         <v>13</v>
       </c>
       <c r="K20" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L20" s="20">
         <v>53</v>
@@ -6233,7 +6230,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>5361</v>
+        <v>5107</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>185</v>
@@ -6277,7 +6274,7 @@
         <v>13</v>
       </c>
       <c r="K21" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L21" s="20">
         <v>48</v>
@@ -6304,7 +6301,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>3306</v>
+        <v>3121</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>185</v>
@@ -6348,7 +6345,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L22" s="20">
         <v>51</v>
@@ -6375,7 +6372,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>4966</v>
+        <v>4842</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>185</v>
@@ -6419,7 +6416,7 @@
         <v>13</v>
       </c>
       <c r="K23" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L23" s="20">
         <v>53</v>
@@ -6446,7 +6443,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4394</v>
+        <v>6438</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>185</v>
@@ -6490,7 +6487,7 @@
         <v>13</v>
       </c>
       <c r="K24" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L24" s="20">
         <v>75</v>
@@ -6517,7 +6514,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4458</v>
+        <v>5339</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>185</v>
@@ -6561,7 +6558,7 @@
         <v>13</v>
       </c>
       <c r="K25" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L25" s="20">
         <v>60</v>
@@ -6588,7 +6585,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4909</v>
+        <v>5216</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>185</v>
@@ -6632,7 +6629,7 @@
         <v>13</v>
       </c>
       <c r="K26" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L26" s="20">
         <v>60</v>
@@ -6659,7 +6656,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>4876</v>
+        <v>5217</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>185</v>
@@ -6703,7 +6700,7 @@
         <v>13</v>
       </c>
       <c r="K27" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L27" s="20">
         <v>54</v>
@@ -6730,7 +6727,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>5758</v>
+        <v>5047</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>185</v>
@@ -6774,7 +6771,7 @@
         <v>13</v>
       </c>
       <c r="K28" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L28" s="20">
         <v>52</v>
@@ -6801,7 +6798,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>3945</v>
+        <v>4050</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>185</v>
@@ -6845,7 +6842,7 @@
         <v>13</v>
       </c>
       <c r="K29" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L29" s="20">
         <v>59</v>
@@ -6872,7 +6869,7 @@
         <v>250</v>
       </c>
       <c r="T29" s="22">
-        <v>4299</v>
+        <v>4619</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>172</v>
@@ -6916,7 +6913,7 @@
         <v>13</v>
       </c>
       <c r="K30" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L30" s="20">
         <v>118</v>
@@ -6943,7 +6940,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>4868</v>
+        <v>4614</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>185</v>
@@ -6987,7 +6984,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L31" s="20">
         <v>76</v>
@@ -7014,7 +7011,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5360</v>
+        <v>4518</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>185</v>
@@ -7058,7 +7055,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L32" s="20">
         <v>72</v>
@@ -7085,7 +7082,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4328</v>
+        <v>4387</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>185</v>
@@ -7129,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="K33" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L33" s="20">
         <v>66</v>
@@ -7156,7 +7153,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>5549</v>
+        <v>5461</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>185</v>
@@ -7200,7 +7197,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L34" s="20">
         <v>68</v>
@@ -7227,7 +7224,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5384</v>
+        <v>5180</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>185</v>
@@ -7271,7 +7268,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L35" s="20">
         <v>62</v>
@@ -7298,7 +7295,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5328</v>
+        <v>6457</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>185</v>
@@ -7342,7 +7339,7 @@
         <v>13</v>
       </c>
       <c r="K36" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L36" s="20">
         <v>56</v>
@@ -7369,7 +7366,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4226</v>
+        <v>4336</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>185</v>
@@ -7413,7 +7410,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L37" s="20">
         <v>61</v>
@@ -7440,7 +7437,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5098</v>
+        <v>4562</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>185</v>
@@ -7482,7 +7479,7 @@
         <v>13</v>
       </c>
       <c r="K38" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L38" s="30">
         <v>0</v>
@@ -7509,7 +7506,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30117</v>
+        <v>30111</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>185</v>
@@ -7553,7 +7550,7 @@
         <v>13</v>
       </c>
       <c r="K39" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L39" s="20">
         <v>61</v>
@@ -7580,7 +7577,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5897</v>
+        <v>5620</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>185</v>
@@ -7624,7 +7621,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L40" s="20">
         <v>47</v>
@@ -7651,7 +7648,7 @@
         <v>275</v>
       </c>
       <c r="T40" s="22">
-        <v>4231</v>
+        <v>4210</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>172</v>
@@ -7695,7 +7692,7 @@
         <v>13</v>
       </c>
       <c r="K41" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L41" s="20">
         <v>47</v>
@@ -7722,7 +7719,7 @@
         <v>279</v>
       </c>
       <c r="T41" s="22">
-        <v>4478</v>
+        <v>4014</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>172</v>
@@ -7766,7 +7763,7 @@
         <v>13</v>
       </c>
       <c r="K42" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L42" s="20">
         <v>47</v>
@@ -7793,7 +7790,7 @@
         <v>284</v>
       </c>
       <c r="T42" s="22">
-        <v>4648</v>
+        <v>5189</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>172</v>
@@ -7837,7 +7834,7 @@
         <v>13</v>
       </c>
       <c r="K43" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L43" s="20">
         <v>47</v>
@@ -7864,7 +7861,7 @@
         <v>288</v>
       </c>
       <c r="T43" s="22">
-        <v>4446</v>
+        <v>4496</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>172</v>
@@ -7908,7 +7905,7 @@
         <v>13</v>
       </c>
       <c r="K44" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L44" s="20">
         <v>47</v>
@@ -7935,7 +7932,7 @@
         <v>292</v>
       </c>
       <c r="T44" s="22">
-        <v>3997</v>
+        <v>4205</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>172</v>
@@ -7979,7 +7976,7 @@
         <v>13</v>
       </c>
       <c r="K45" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L45" s="20">
         <v>57</v>
@@ -8006,7 +8003,7 @@
         <v>299</v>
       </c>
       <c r="T45" s="22">
-        <v>4008</v>
+        <v>4730</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>172</v>
@@ -8050,7 +8047,7 @@
         <v>13</v>
       </c>
       <c r="K46" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L46" s="20">
         <v>52</v>
@@ -8077,7 +8074,7 @@
         <v>304</v>
       </c>
       <c r="T46" s="22">
-        <v>3949</v>
+        <v>4074</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>172</v>
@@ -8121,7 +8118,7 @@
         <v>13</v>
       </c>
       <c r="K47" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L47" s="20">
         <v>47</v>
@@ -8148,7 +8145,7 @@
         <v>309</v>
       </c>
       <c r="T47" s="22">
-        <v>4874</v>
+        <v>3775</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>172</v>
@@ -8192,7 +8189,7 @@
         <v>13</v>
       </c>
       <c r="K48" s="20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L48" s="20">
         <v>47</v>
@@ -8219,7 +8216,7 @@
         <v>316</v>
       </c>
       <c r="T48" s="22">
-        <v>3864</v>
+        <v>4263</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>172</v>
@@ -8290,7 +8287,7 @@
         <v>321</v>
       </c>
       <c r="T49" s="22">
-        <v>4250</v>
+        <v>4995</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>172</v>
@@ -8361,7 +8358,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5106</v>
+        <v>5166</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>185</v>
@@ -8408,7 +8405,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="20">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M51" s="21">
         <v>36</v>
@@ -8432,7 +8429,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>14384</v>
+        <v>5040</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>185</v>
@@ -8476,7 +8473,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L52" s="20">
         <v>82</v>
@@ -8503,7 +8500,7 @@
         <v>13</v>
       </c>
       <c r="T52" s="22">
-        <v>4864</v>
+        <v>5044</v>
       </c>
       <c r="U52" s="25" t="s">
         <v>185</v>
@@ -8574,7 +8571,7 @@
         <v>13</v>
       </c>
       <c r="T53" s="22">
-        <v>4248</v>
+        <v>4311</v>
       </c>
       <c r="U53" s="25" t="s">
         <v>185</v>
@@ -8645,7 +8642,7 @@
         <v>13</v>
       </c>
       <c r="T54" s="22">
-        <v>4451</v>
+        <v>4486</v>
       </c>
       <c r="U54" s="25" t="s">
         <v>185</v>
@@ -8689,7 +8686,7 @@
         <v>13</v>
       </c>
       <c r="K55" s="20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L55" s="20">
         <v>59</v>
@@ -8716,7 +8713,7 @@
         <v>13</v>
       </c>
       <c r="T55" s="22">
-        <v>4965</v>
+        <v>5310</v>
       </c>
       <c r="U55" s="25" t="s">
         <v>185</v>
@@ -8787,7 +8784,7 @@
         <v>13</v>
       </c>
       <c r="T56" s="22">
-        <v>4826</v>
+        <v>4510</v>
       </c>
       <c r="U56" s="25" t="s">
         <v>185</v>
@@ -8858,7 +8855,7 @@
         <v>13</v>
       </c>
       <c r="T57" s="22">
-        <v>4343</v>
+        <v>4434</v>
       </c>
       <c r="U57" s="25" t="s">
         <v>185</v>
@@ -8929,7 +8926,7 @@
         <v>13</v>
       </c>
       <c r="T58" s="22">
-        <v>6040</v>
+        <v>4945</v>
       </c>
       <c r="U58" s="25" t="s">
         <v>185</v>
@@ -9000,7 +8997,7 @@
         <v>13</v>
       </c>
       <c r="T59" s="22">
-        <v>5170</v>
+        <v>4872</v>
       </c>
       <c r="U59" s="25" t="s">
         <v>185</v>
@@ -9044,7 +9041,7 @@
         <v>13</v>
       </c>
       <c r="K60" s="20">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L60" s="20">
         <v>47</v>
@@ -9071,7 +9068,7 @@
         <v>346</v>
       </c>
       <c r="T60" s="22">
-        <v>4316</v>
+        <v>4279</v>
       </c>
       <c r="U60" s="19" t="s">
         <v>172</v>
@@ -9115,7 +9112,7 @@
         <v>13</v>
       </c>
       <c r="K61" s="20">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L61" s="20">
         <v>59</v>
@@ -9142,7 +9139,7 @@
         <v>13</v>
       </c>
       <c r="T61" s="22">
-        <v>4376</v>
+        <v>4820</v>
       </c>
       <c r="U61" s="25" t="s">
         <v>185</v>
@@ -9213,7 +9210,7 @@
         <v>13</v>
       </c>
       <c r="T62" s="22">
-        <v>4922</v>
+        <v>5040</v>
       </c>
       <c r="U62" s="25" t="s">
         <v>185</v>
@@ -9284,7 +9281,7 @@
         <v>13</v>
       </c>
       <c r="T63" s="22">
-        <v>4281</v>
+        <v>4182</v>
       </c>
       <c r="U63" s="25" t="s">
         <v>185</v>
@@ -9355,7 +9352,7 @@
         <v>13</v>
       </c>
       <c r="T64" s="22">
-        <v>4845</v>
+        <v>3827</v>
       </c>
       <c r="U64" s="25" t="s">
         <v>185</v>
@@ -9426,7 +9423,7 @@
         <v>13</v>
       </c>
       <c r="T65" s="22">
-        <v>4973</v>
+        <v>5999</v>
       </c>
       <c r="U65" s="25" t="s">
         <v>185</v>
@@ -9497,7 +9494,7 @@
         <v>13</v>
       </c>
       <c r="T66" s="22">
-        <v>5207</v>
+        <v>5458</v>
       </c>
       <c r="U66" s="25" t="s">
         <v>185</v>
@@ -9568,7 +9565,7 @@
         <v>13</v>
       </c>
       <c r="T67" s="22">
-        <v>4506</v>
+        <v>3999</v>
       </c>
       <c r="U67" s="25" t="s">
         <v>185</v>
@@ -9639,7 +9636,7 @@
         <v>13</v>
       </c>
       <c r="T68" s="22">
-        <v>5409</v>
+        <v>7271</v>
       </c>
       <c r="U68" s="25" t="s">
         <v>185</v>
@@ -9710,7 +9707,7 @@
         <v>13</v>
       </c>
       <c r="T69" s="22">
-        <v>5403</v>
+        <v>5371</v>
       </c>
       <c r="U69" s="25" t="s">
         <v>185</v>
@@ -9781,7 +9778,7 @@
         <v>13</v>
       </c>
       <c r="T70" s="22">
-        <v>8600</v>
+        <v>4967</v>
       </c>
       <c r="U70" s="25" t="s">
         <v>185</v>
@@ -9852,7 +9849,7 @@
         <v>13</v>
       </c>
       <c r="T71" s="22">
-        <v>5096</v>
+        <v>4805</v>
       </c>
       <c r="U71" s="25" t="s">
         <v>185</v>
@@ -9923,7 +9920,7 @@
         <v>13</v>
       </c>
       <c r="T72" s="22">
-        <v>5124</v>
+        <v>4512</v>
       </c>
       <c r="U72" s="25" t="s">
         <v>185</v>
@@ -9994,7 +9991,7 @@
         <v>13</v>
       </c>
       <c r="T73" s="22">
-        <v>4699</v>
+        <v>4357</v>
       </c>
       <c r="U73" s="25" t="s">
         <v>185</v>
@@ -10065,7 +10062,7 @@
         <v>13</v>
       </c>
       <c r="T74" s="22">
-        <v>5378</v>
+        <v>5444</v>
       </c>
       <c r="U74" s="25" t="s">
         <v>185</v>
@@ -10136,7 +10133,7 @@
         <v>13</v>
       </c>
       <c r="T75" s="22">
-        <v>5839</v>
+        <v>5244</v>
       </c>
       <c r="U75" s="25" t="s">
         <v>185</v>
@@ -10207,7 +10204,7 @@
         <v>13</v>
       </c>
       <c r="T76" s="22">
-        <v>5554</v>
+        <v>5065</v>
       </c>
       <c r="U76" s="25" t="s">
         <v>185</v>
@@ -10278,7 +10275,7 @@
         <v>13</v>
       </c>
       <c r="T77" s="22">
-        <v>5728</v>
+        <v>5042</v>
       </c>
       <c r="U77" s="25" t="s">
         <v>185</v>
@@ -10349,7 +10346,7 @@
         <v>13</v>
       </c>
       <c r="T78" s="22">
-        <v>4292</v>
+        <v>4582</v>
       </c>
       <c r="U78" s="25" t="s">
         <v>185</v>
@@ -10420,7 +10417,7 @@
         <v>13</v>
       </c>
       <c r="T79" s="22">
-        <v>5053</v>
+        <v>5128</v>
       </c>
       <c r="U79" s="25" t="s">
         <v>185</v>
@@ -10491,7 +10488,7 @@
         <v>13</v>
       </c>
       <c r="T80" s="22">
-        <v>4474</v>
+        <v>8230</v>
       </c>
       <c r="U80" s="25" t="s">
         <v>185</v>
@@ -10508,10 +10505,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81" s="18" t="s">
         <v>384</v>
-      </c>
-      <c r="C81" s="18" t="s">
-        <v>385</v>
       </c>
       <c r="D81" t="s">
         <v>333</v>
@@ -10520,14 +10517,12 @@
         <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="G81" t="s">
         <v>13</v>
       </c>
-      <c r="H81" s="19">
-        <v>200</v>
-      </c>
+      <c r="H81" s="17"/>
       <c r="I81" s="17" t="s">
         <v>13</v>
       </c>
@@ -10535,16 +10530,16 @@
         <v>13</v>
       </c>
       <c r="K81" s="20">
-        <v>6</v>
-      </c>
-      <c r="L81" s="20">
-        <v>61</v>
-      </c>
-      <c r="M81" s="21">
-        <v>25</v>
-      </c>
-      <c r="N81" s="28">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="L81" s="30">
+        <v>0</v>
+      </c>
+      <c r="M81" s="31">
+        <v>0</v>
+      </c>
+      <c r="N81" s="20">
+        <v>0</v>
       </c>
       <c r="O81" s="17" t="s">
         <v>13</v>
@@ -10562,13 +10557,13 @@
         <v>13</v>
       </c>
       <c r="T81" s="22">
-        <v>28394</v>
+        <v>30137</v>
       </c>
       <c r="U81" s="25" t="s">
         <v>185</v>
       </c>
       <c r="V81" s="26">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="W81" s="27" t="s">
         <v>186</v>
@@ -10579,10 +10574,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>385</v>
+      </c>
+      <c r="C82" s="18" t="s">
         <v>386</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>387</v>
       </c>
       <c r="D82" t="s">
         <v>182</v>
@@ -10633,7 +10628,7 @@
         <v>13</v>
       </c>
       <c r="T82" s="22">
-        <v>4242</v>
+        <v>4572</v>
       </c>
       <c r="U82" s="25" t="s">
         <v>185</v>
@@ -10650,10 +10645,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>387</v>
+      </c>
+      <c r="C83" s="18" t="s">
         <v>388</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>389</v>
       </c>
       <c r="D83" t="s">
         <v>182</v>
@@ -10704,7 +10699,7 @@
         <v>13</v>
       </c>
       <c r="T83" s="22">
-        <v>4397</v>
+        <v>4514</v>
       </c>
       <c r="U83" s="25" t="s">
         <v>185</v>
@@ -10721,10 +10716,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>389</v>
+      </c>
+      <c r="C84" s="18" t="s">
         <v>390</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>391</v>
       </c>
       <c r="D84" t="s">
         <v>252</v>
@@ -10775,7 +10770,7 @@
         <v>13</v>
       </c>
       <c r="T84" s="22">
-        <v>4386</v>
+        <v>4782</v>
       </c>
       <c r="U84" s="25" t="s">
         <v>185</v>
@@ -10792,10 +10787,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>391</v>
+      </c>
+      <c r="C85" s="18" t="s">
         <v>392</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>393</v>
       </c>
       <c r="D85" t="s">
         <v>13</v>
@@ -10804,7 +10799,7 @@
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G85" t="s">
         <v>13</v>
@@ -10846,7 +10841,7 @@
         <v>13</v>
       </c>
       <c r="T85" s="22">
-        <v>1323</v>
+        <v>1228</v>
       </c>
       <c r="U85" s="25" t="s">
         <v>185</v>
@@ -10863,10 +10858,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>394</v>
+      </c>
+      <c r="C86" s="18" t="s">
         <v>395</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>396</v>
       </c>
       <c r="D86" t="s">
         <v>252</v>
@@ -10917,7 +10912,7 @@
         <v>13</v>
       </c>
       <c r="T86" s="22">
-        <v>5170</v>
+        <v>5386</v>
       </c>
       <c r="U86" s="25" t="s">
         <v>185</v>
@@ -10934,13 +10929,13 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>396</v>
+      </c>
+      <c r="C87" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C87" s="18" t="s">
-        <v>398</v>
-      </c>
       <c r="D87" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E87" s="17">
         <v>2</v>
@@ -10964,7 +10959,7 @@
         <v>7</v>
       </c>
       <c r="L87" s="20">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M87" s="21">
         <v>40</v>
@@ -10988,7 +10983,7 @@
         <v>13</v>
       </c>
       <c r="T87" s="22">
-        <v>15364</v>
+        <v>5198</v>
       </c>
       <c r="U87" s="25" t="s">
         <v>185</v>
@@ -11005,13 +11000,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>398</v>
+      </c>
+      <c r="C88" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="C88" s="18" t="s">
-        <v>400</v>
-      </c>
       <c r="D88" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E88" s="17">
         <v>2</v>
@@ -11059,7 +11054,7 @@
         <v>13</v>
       </c>
       <c r="T88" s="22">
-        <v>4682</v>
+        <v>4454</v>
       </c>
       <c r="U88" s="25" t="s">
         <v>185</v>
@@ -11076,13 +11071,13 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>400</v>
+      </c>
+      <c r="C89" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="C89" s="18" t="s">
-        <v>402</v>
-      </c>
       <c r="D89" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E89" s="17">
         <v>2</v>
@@ -11130,7 +11125,7 @@
         <v>13</v>
       </c>
       <c r="T89" s="22">
-        <v>4731</v>
+        <v>4107</v>
       </c>
       <c r="U89" s="25" t="s">
         <v>185</v>
@@ -11147,13 +11142,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>402</v>
+      </c>
+      <c r="C90" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="C90" s="18" t="s">
-        <v>404</v>
-      </c>
       <c r="D90" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E90" s="17">
         <v>2</v>
@@ -11201,7 +11196,7 @@
         <v>13</v>
       </c>
       <c r="T90" s="22">
-        <v>5361</v>
+        <v>4294</v>
       </c>
       <c r="U90" s="25" t="s">
         <v>185</v>
@@ -11218,10 +11213,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>404</v>
+      </c>
+      <c r="C91" s="18" t="s">
         <v>405</v>
-      </c>
-      <c r="C91" s="18" t="s">
-        <v>406</v>
       </c>
       <c r="D91" t="s">
         <v>252</v>
@@ -11272,7 +11267,7 @@
         <v>13</v>
       </c>
       <c r="T91" s="22">
-        <v>7859</v>
+        <v>5448</v>
       </c>
       <c r="U91" s="25" t="s">
         <v>185</v>
@@ -11292,7 +11287,7 @@
         <v>224</v>
       </c>
       <c r="C92" s="18" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D92" t="s">
         <v>13</v>
@@ -11343,7 +11338,7 @@
         <v>13</v>
       </c>
       <c r="T92" s="22">
-        <v>4309</v>
+        <v>4124</v>
       </c>
       <c r="U92" s="25" t="s">
         <v>185</v>
@@ -11363,10 +11358,10 @@
         <v>204</v>
       </c>
       <c r="C93" s="18" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D93" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E93" s="17">
         <v>2</v>
@@ -11414,7 +11409,7 @@
         <v>13</v>
       </c>
       <c r="T93" s="22">
-        <v>8502</v>
+        <v>4266</v>
       </c>
       <c r="U93" s="25" t="s">
         <v>185</v>
@@ -11431,13 +11426,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>408</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>409</v>
       </c>
-      <c r="C94" s="18" t="s">
-        <v>410</v>
-      </c>
       <c r="D94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E94" s="17">
         <v>2</v>
@@ -11485,7 +11480,7 @@
         <v>13</v>
       </c>
       <c r="T94" s="22">
-        <v>4934</v>
+        <v>4442</v>
       </c>
       <c r="U94" s="25" t="s">
         <v>185</v>
@@ -11502,13 +11497,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>410</v>
+      </c>
+      <c r="C95" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="C95" s="18" t="s">
-        <v>412</v>
-      </c>
       <c r="D95" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E95" s="17">
         <v>2</v>
@@ -11556,7 +11551,7 @@
         <v>13</v>
       </c>
       <c r="T95" s="22">
-        <v>4485</v>
+        <v>4456</v>
       </c>
       <c r="U95" s="25" t="s">
         <v>185</v>
@@ -11573,13 +11568,13 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="C96" s="18" t="s">
-        <v>414</v>
-      </c>
       <c r="D96" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E96" s="17">
         <v>2</v>
@@ -11627,7 +11622,7 @@
         <v>13</v>
       </c>
       <c r="T96" s="22">
-        <v>4748</v>
+        <v>4441</v>
       </c>
       <c r="U96" s="25" t="s">
         <v>185</v>
@@ -11644,10 +11639,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>414</v>
+      </c>
+      <c r="C97" s="18" t="s">
         <v>415</v>
-      </c>
-      <c r="C97" s="18" t="s">
-        <v>416</v>
       </c>
       <c r="D97" t="s">
         <v>252</v>
@@ -11698,7 +11693,7 @@
         <v>13</v>
       </c>
       <c r="T97" s="22">
-        <v>5594</v>
+        <v>4792</v>
       </c>
       <c r="U97" s="25" t="s">
         <v>185</v>
@@ -11715,10 +11710,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>416</v>
+      </c>
+      <c r="C98" s="18" t="s">
         <v>417</v>
-      </c>
-      <c r="C98" s="18" t="s">
-        <v>418</v>
       </c>
       <c r="D98" t="s">
         <v>189</v>
@@ -11769,7 +11764,7 @@
         <v>13</v>
       </c>
       <c r="T98" s="22">
-        <v>10007</v>
+        <v>5305</v>
       </c>
       <c r="U98" s="25" t="s">
         <v>185</v>
@@ -11786,10 +11781,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>418</v>
+      </c>
+      <c r="C99" s="18" t="s">
         <v>419</v>
-      </c>
-      <c r="C99" s="18" t="s">
-        <v>420</v>
       </c>
       <c r="D99" t="s">
         <v>189</v>
@@ -11840,7 +11835,7 @@
         <v>13</v>
       </c>
       <c r="T99" s="22">
-        <v>5378</v>
+        <v>5280</v>
       </c>
       <c r="U99" s="25" t="s">
         <v>185</v>
@@ -11857,10 +11852,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>420</v>
+      </c>
+      <c r="C100" s="18" t="s">
         <v>421</v>
-      </c>
-      <c r="C100" s="18" t="s">
-        <v>422</v>
       </c>
       <c r="D100" t="s">
         <v>189</v>
@@ -11911,7 +11906,7 @@
         <v>13</v>
       </c>
       <c r="T100" s="22">
-        <v>5063</v>
+        <v>6699</v>
       </c>
       <c r="U100" s="25" t="s">
         <v>185</v>
@@ -11928,10 +11923,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>422</v>
+      </c>
+      <c r="C101" s="18" t="s">
         <v>423</v>
-      </c>
-      <c r="C101" s="18" t="s">
-        <v>424</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
@@ -11940,7 +11935,7 @@
         <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G101" t="s">
         <v>13</v>
@@ -11982,7 +11977,7 @@
         <v>13</v>
       </c>
       <c r="T101" s="22">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="U101" s="25" t="s">
         <v>185</v>
@@ -12127,10 +12122,10 @@
         <v>156</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>425</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -12144,7 +12139,7 @@
         <v>170</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>173</v>
@@ -12161,7 +12156,7 @@
         <v>170</v>
       </c>
       <c r="D3" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E3" s="32" t="s">
         <v>173</v>
@@ -12178,7 +12173,7 @@
         <v>184</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E4" s="33" t="s">
         <v>186</v>
@@ -12195,7 +12190,7 @@
         <v>184</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E5" s="33" t="s">
         <v>186</v>
@@ -12212,7 +12207,7 @@
         <v>184</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E6" s="33" t="s">
         <v>186</v>
@@ -12229,7 +12224,7 @@
         <v>184</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>186</v>
@@ -12246,7 +12241,7 @@
         <v>184</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E8" s="33" t="s">
         <v>186</v>
@@ -12263,7 +12258,7 @@
         <v>184</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>186</v>
@@ -12280,7 +12275,7 @@
         <v>184</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E10" s="33" t="s">
         <v>186</v>
@@ -12297,7 +12292,7 @@
         <v>184</v>
       </c>
       <c r="D11" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E11" s="33" t="s">
         <v>186</v>
@@ -12314,7 +12309,7 @@
         <v>170</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E12" s="32" t="s">
         <v>173</v>
@@ -12331,7 +12326,7 @@
         <v>184</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>186</v>
@@ -12348,7 +12343,7 @@
         <v>184</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>186</v>
@@ -12365,7 +12360,7 @@
         <v>170</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E15" s="32" t="s">
         <v>173</v>
@@ -12382,7 +12377,7 @@
         <v>184</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>186</v>
@@ -12399,7 +12394,7 @@
         <v>184</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>186</v>
@@ -12416,7 +12411,7 @@
         <v>184</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>186</v>
@@ -12433,7 +12428,7 @@
         <v>184</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>186</v>
@@ -12450,7 +12445,7 @@
         <v>184</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E20" s="33" t="s">
         <v>186</v>
@@ -12467,7 +12462,7 @@
         <v>184</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E21" s="34" t="s">
         <v>232</v>
@@ -12484,7 +12479,7 @@
         <v>184</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E22" s="33" t="s">
         <v>186</v>
@@ -12501,7 +12496,7 @@
         <v>184</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E23" s="33" t="s">
         <v>186</v>
@@ -12518,7 +12513,7 @@
         <v>184</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E24" s="33" t="s">
         <v>186</v>
@@ -12535,7 +12530,7 @@
         <v>184</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E25" s="33" t="s">
         <v>186</v>
@@ -12552,7 +12547,7 @@
         <v>184</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>186</v>
@@ -12569,7 +12564,7 @@
         <v>184</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E27" s="33" t="s">
         <v>186</v>
@@ -12586,7 +12581,7 @@
         <v>184</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E28" s="33" t="s">
         <v>186</v>
@@ -12603,7 +12598,7 @@
         <v>170</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E29" s="32" t="s">
         <v>173</v>
@@ -12620,7 +12615,7 @@
         <v>184</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E30" s="33" t="s">
         <v>186</v>
@@ -12637,7 +12632,7 @@
         <v>184</v>
       </c>
       <c r="D31" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E31" s="33" t="s">
         <v>186</v>
@@ -12654,7 +12649,7 @@
         <v>184</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E32" s="33" t="s">
         <v>186</v>
@@ -12671,7 +12666,7 @@
         <v>184</v>
       </c>
       <c r="D33" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E33" s="33" t="s">
         <v>186</v>
@@ -12688,7 +12683,7 @@
         <v>184</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>186</v>
@@ -12705,7 +12700,7 @@
         <v>184</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E35" s="33" t="s">
         <v>186</v>
@@ -12722,7 +12717,7 @@
         <v>184</v>
       </c>
       <c r="D36" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E36" s="33" t="s">
         <v>186</v>
@@ -12739,7 +12734,7 @@
         <v>184</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E37" s="33" t="s">
         <v>186</v>
@@ -12756,7 +12751,7 @@
         <v>184</v>
       </c>
       <c r="D38" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>186</v>
@@ -12773,7 +12768,7 @@
         <v>184</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E39" s="33" t="s">
         <v>186</v>
@@ -12790,7 +12785,7 @@
         <v>170</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E40" s="32" t="s">
         <v>173</v>
@@ -12807,7 +12802,7 @@
         <v>170</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E41" s="32" t="s">
         <v>173</v>
@@ -12824,7 +12819,7 @@
         <v>170</v>
       </c>
       <c r="D42" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E42" s="32" t="s">
         <v>173</v>
@@ -12841,7 +12836,7 @@
         <v>170</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E43" s="32" t="s">
         <v>173</v>
@@ -12858,7 +12853,7 @@
         <v>170</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E44" s="32" t="s">
         <v>173</v>
@@ -12875,7 +12870,7 @@
         <v>298</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E45" s="32" t="s">
         <v>173</v>
@@ -12892,7 +12887,7 @@
         <v>170</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E46" s="32" t="s">
         <v>173</v>
@@ -12909,7 +12904,7 @@
         <v>170</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E47" s="32" t="s">
         <v>173</v>
@@ -12926,7 +12921,7 @@
         <v>315</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E48" s="32" t="s">
         <v>173</v>
@@ -12943,7 +12938,7 @@
         <v>170</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E49" s="32" t="s">
         <v>173</v>
@@ -12960,7 +12955,7 @@
         <v>184</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E50" s="33" t="s">
         <v>186</v>
@@ -12977,7 +12972,7 @@
         <v>184</v>
       </c>
       <c r="D51" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E51" s="33" t="s">
         <v>186</v>
@@ -12994,7 +12989,7 @@
         <v>184</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E52" s="33" t="s">
         <v>186</v>
@@ -13011,7 +13006,7 @@
         <v>184</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>186</v>
@@ -13028,7 +13023,7 @@
         <v>184</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>186</v>
@@ -13045,7 +13040,7 @@
         <v>184</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>186</v>
@@ -13062,7 +13057,7 @@
         <v>184</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>186</v>
@@ -13079,7 +13074,7 @@
         <v>184</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>186</v>
@@ -13096,7 +13091,7 @@
         <v>184</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>186</v>
@@ -13113,7 +13108,7 @@
         <v>184</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>186</v>
@@ -13130,7 +13125,7 @@
         <v>170</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E60" s="32" t="s">
         <v>173</v>
@@ -13147,7 +13142,7 @@
         <v>184</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>186</v>
@@ -13164,7 +13159,7 @@
         <v>184</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>186</v>
@@ -13181,7 +13176,7 @@
         <v>184</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>186</v>
@@ -13198,7 +13193,7 @@
         <v>184</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>186</v>
@@ -13215,7 +13210,7 @@
         <v>184</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>186</v>
@@ -13232,7 +13227,7 @@
         <v>184</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>186</v>
@@ -13249,7 +13244,7 @@
         <v>184</v>
       </c>
       <c r="D67" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>186</v>
@@ -13266,7 +13261,7 @@
         <v>184</v>
       </c>
       <c r="D68" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>186</v>
@@ -13283,7 +13278,7 @@
         <v>184</v>
       </c>
       <c r="D69" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>186</v>
@@ -13300,7 +13295,7 @@
         <v>184</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>186</v>
@@ -13317,7 +13312,7 @@
         <v>184</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>186</v>
@@ -13334,7 +13329,7 @@
         <v>184</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>186</v>
@@ -13351,7 +13346,7 @@
         <v>184</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E73" s="33" t="s">
         <v>186</v>
@@ -13368,7 +13363,7 @@
         <v>184</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E74" s="33" t="s">
         <v>186</v>
@@ -13385,7 +13380,7 @@
         <v>184</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E75" s="33" t="s">
         <v>186</v>
@@ -13402,7 +13397,7 @@
         <v>184</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E76" s="33" t="s">
         <v>186</v>
@@ -13419,7 +13414,7 @@
         <v>184</v>
       </c>
       <c r="D77" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E77" s="33" t="s">
         <v>186</v>
@@ -13436,7 +13431,7 @@
         <v>184</v>
       </c>
       <c r="D78" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E78" s="33" t="s">
         <v>186</v>
@@ -13453,7 +13448,7 @@
         <v>184</v>
       </c>
       <c r="D79" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E79" s="33" t="s">
         <v>186</v>
@@ -13470,7 +13465,7 @@
         <v>184</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E80" s="33" t="s">
         <v>186</v>
@@ -13478,7 +13473,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>384</v>
+        <v>267</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -13487,7 +13482,7 @@
         <v>184</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E81" s="33" t="s">
         <v>186</v>
@@ -13495,7 +13490,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -13504,7 +13499,7 @@
         <v>184</v>
       </c>
       <c r="D82" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>186</v>
@@ -13512,7 +13507,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -13521,7 +13516,7 @@
         <v>184</v>
       </c>
       <c r="D83" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E83" s="33" t="s">
         <v>186</v>
@@ -13529,7 +13524,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -13538,7 +13533,7 @@
         <v>184</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>186</v>
@@ -13546,7 +13541,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -13555,7 +13550,7 @@
         <v>184</v>
       </c>
       <c r="D85" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>186</v>
@@ -13563,7 +13558,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -13572,7 +13567,7 @@
         <v>184</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>186</v>
@@ -13580,7 +13575,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -13589,7 +13584,7 @@
         <v>184</v>
       </c>
       <c r="D87" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E87" s="33" t="s">
         <v>186</v>
@@ -13597,7 +13592,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -13606,7 +13601,7 @@
         <v>184</v>
       </c>
       <c r="D88" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E88" s="33" t="s">
         <v>186</v>
@@ -13614,7 +13609,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -13623,7 +13618,7 @@
         <v>184</v>
       </c>
       <c r="D89" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E89" s="33" t="s">
         <v>186</v>
@@ -13631,7 +13626,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -13640,7 +13635,7 @@
         <v>184</v>
       </c>
       <c r="D90" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E90" s="33" t="s">
         <v>186</v>
@@ -13648,7 +13643,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -13657,7 +13652,7 @@
         <v>184</v>
       </c>
       <c r="D91" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E91" s="33" t="s">
         <v>186</v>
@@ -13674,7 +13669,7 @@
         <v>184</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E92" s="33" t="s">
         <v>186</v>
@@ -13691,7 +13686,7 @@
         <v>184</v>
       </c>
       <c r="D93" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E93" s="33" t="s">
         <v>186</v>
@@ -13699,7 +13694,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -13708,7 +13703,7 @@
         <v>184</v>
       </c>
       <c r="D94" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E94" s="33" t="s">
         <v>186</v>
@@ -13716,7 +13711,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -13725,7 +13720,7 @@
         <v>184</v>
       </c>
       <c r="D95" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E95" s="33" t="s">
         <v>186</v>
@@ -13733,7 +13728,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -13742,7 +13737,7 @@
         <v>184</v>
       </c>
       <c r="D96" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E96" s="33" t="s">
         <v>186</v>
@@ -13750,7 +13745,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -13759,7 +13754,7 @@
         <v>184</v>
       </c>
       <c r="D97" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E97" s="33" t="s">
         <v>186</v>
@@ -13767,7 +13762,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -13776,7 +13771,7 @@
         <v>184</v>
       </c>
       <c r="D98" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E98" s="33" t="s">
         <v>186</v>
@@ -13784,7 +13779,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -13793,7 +13788,7 @@
         <v>184</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E99" s="33" t="s">
         <v>186</v>
@@ -13801,7 +13796,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -13810,7 +13805,7 @@
         <v>184</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E100" s="33" t="s">
         <v>186</v>
@@ -13818,7 +13813,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -13827,7 +13822,7 @@
         <v>184</v>
       </c>
       <c r="D101" s="32" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E101" s="33" t="s">
         <v>186</v>
@@ -13857,7 +13852,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>140</v>
@@ -13925,13 +13920,13 @@
         <v>141</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>148</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>142</v>
@@ -14011,7 +14006,7 @@
         <v>150</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -14022,13 +14017,13 @@
         <v>163</v>
       </c>
       <c r="C2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <v>59</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -14039,13 +14034,13 @@
         <v>175</v>
       </c>
       <c r="C3">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>48</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -14056,13 +14051,13 @@
         <v>182</v>
       </c>
       <c r="C4">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D4">
         <v>75</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -14073,13 +14068,13 @@
         <v>188</v>
       </c>
       <c r="C5">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5">
         <v>66</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -14090,13 +14085,13 @@
         <v>192</v>
       </c>
       <c r="C6">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D6">
         <v>61</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -14107,13 +14102,13 @@
         <v>194</v>
       </c>
       <c r="C7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7">
         <v>58</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -14124,13 +14119,13 @@
         <v>197</v>
       </c>
       <c r="C8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D8">
         <v>62</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -14141,13 +14136,13 @@
         <v>200</v>
       </c>
       <c r="C9">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9">
         <v>56</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -14158,13 +14153,13 @@
         <v>203</v>
       </c>
       <c r="C10">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10">
         <v>55</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -14175,13 +14170,13 @@
         <v>205</v>
       </c>
       <c r="C11">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11">
         <v>56</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -14192,13 +14187,13 @@
         <v>207</v>
       </c>
       <c r="C12">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <v>70</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -14209,13 +14204,13 @@
         <v>212</v>
       </c>
       <c r="C13">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>60</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -14226,13 +14221,13 @@
         <v>214</v>
       </c>
       <c r="C14">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14">
         <v>56</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -14243,13 +14238,13 @@
         <v>216</v>
       </c>
       <c r="C15">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D15">
         <v>85</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -14260,13 +14255,13 @@
         <v>220</v>
       </c>
       <c r="C16">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D16">
         <v>59</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -14277,13 +14272,13 @@
         <v>222</v>
       </c>
       <c r="C17">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17">
         <v>57</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -14294,13 +14289,13 @@
         <v>189</v>
       </c>
       <c r="C18">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D18">
         <v>82</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -14311,13 +14306,13 @@
         <v>226</v>
       </c>
       <c r="C19">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D19">
         <v>63</v>
       </c>
       <c r="E19" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -14328,13 +14323,13 @@
         <v>228</v>
       </c>
       <c r="C20">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20">
         <v>53</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -14345,13 +14340,13 @@
         <v>230</v>
       </c>
       <c r="C21">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21">
         <v>48</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -14362,13 +14357,13 @@
         <v>234</v>
       </c>
       <c r="C22">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22">
         <v>51</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -14379,13 +14374,13 @@
         <v>236</v>
       </c>
       <c r="C23">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23">
         <v>53</v>
       </c>
       <c r="E23" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -14396,13 +14391,13 @@
         <v>238</v>
       </c>
       <c r="C24">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24">
         <v>75</v>
       </c>
       <c r="E24" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -14413,13 +14408,13 @@
         <v>240</v>
       </c>
       <c r="C25">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25">
         <v>60</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -14430,13 +14425,13 @@
         <v>242</v>
       </c>
       <c r="C26">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26">
         <v>60</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -14447,13 +14442,13 @@
         <v>244</v>
       </c>
       <c r="C27">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27">
         <v>54</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -14464,13 +14459,13 @@
         <v>246</v>
       </c>
       <c r="C28">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28">
         <v>52</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -14481,13 +14476,13 @@
         <v>248</v>
       </c>
       <c r="C29">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D29">
         <v>59</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -14498,13 +14493,13 @@
         <v>252</v>
       </c>
       <c r="C30">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D30">
         <v>118</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -14515,13 +14510,13 @@
         <v>254</v>
       </c>
       <c r="C31">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31">
         <v>76</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -14532,13 +14527,13 @@
         <v>195</v>
       </c>
       <c r="C32">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D32">
         <v>72</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -14549,13 +14544,13 @@
         <v>258</v>
       </c>
       <c r="C33">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33">
         <v>66</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -14566,13 +14561,13 @@
         <v>260</v>
       </c>
       <c r="C34">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34">
         <v>68</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -14583,13 +14578,13 @@
         <v>262</v>
       </c>
       <c r="C35">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D35">
         <v>62</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -14600,13 +14595,13 @@
         <v>264</v>
       </c>
       <c r="C36">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36">
         <v>56</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -14617,13 +14612,13 @@
         <v>266</v>
       </c>
       <c r="C37">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D37">
         <v>61</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -14634,13 +14629,13 @@
         <v>268</v>
       </c>
       <c r="C38">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -14651,13 +14646,13 @@
         <v>270</v>
       </c>
       <c r="C39">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D39">
         <v>61</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -14668,13 +14663,13 @@
         <v>272</v>
       </c>
       <c r="C40">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D40">
         <v>47</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -14685,13 +14680,13 @@
         <v>277</v>
       </c>
       <c r="C41">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41">
         <v>47</v>
       </c>
       <c r="E41" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -14702,13 +14697,13 @@
         <v>281</v>
       </c>
       <c r="C42">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D42">
         <v>47</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -14719,13 +14714,13 @@
         <v>286</v>
       </c>
       <c r="C43">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D43">
         <v>47</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -14736,13 +14731,13 @@
         <v>290</v>
       </c>
       <c r="C44">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D44">
         <v>47</v>
       </c>
       <c r="E44" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -14753,13 +14748,13 @@
         <v>294</v>
       </c>
       <c r="C45">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D45">
         <v>57</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -14770,13 +14765,13 @@
         <v>301</v>
       </c>
       <c r="C46">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D46">
         <v>52</v>
       </c>
       <c r="E46" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -14787,13 +14782,13 @@
         <v>306</v>
       </c>
       <c r="C47">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D47">
         <v>47</v>
       </c>
       <c r="E47" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -14804,13 +14799,13 @@
         <v>311</v>
       </c>
       <c r="C48">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D48">
         <v>47</v>
       </c>
       <c r="E48" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -14827,7 +14822,7 @@
         <v>68</v>
       </c>
       <c r="E49" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -14844,7 +14839,7 @@
         <v>68</v>
       </c>
       <c r="E50" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -14858,10 +14853,10 @@
         <v>23</v>
       </c>
       <c r="D51">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E51" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -14872,13 +14867,13 @@
         <v>327</v>
       </c>
       <c r="C52">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52">
         <v>82</v>
       </c>
       <c r="E52" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -14895,7 +14890,7 @@
         <v>52</v>
       </c>
       <c r="E53" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -14912,7 +14907,7 @@
         <v>58</v>
       </c>
       <c r="E54" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -14923,13 +14918,13 @@
         <v>333</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>59</v>
       </c>
       <c r="E55" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -14946,7 +14941,7 @@
         <v>64</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -14963,7 +14958,7 @@
         <v>88</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -14980,7 +14975,7 @@
         <v>53</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -14997,7 +14992,7 @@
         <v>60</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -15008,13 +15003,13 @@
         <v>343</v>
       </c>
       <c r="C60">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D60">
         <v>47</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -15025,13 +15020,13 @@
         <v>348</v>
       </c>
       <c r="C61">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61">
         <v>59</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -15048,7 +15043,7 @@
         <v>52</v>
       </c>
       <c r="E62" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -15065,7 +15060,7 @@
         <v>49</v>
       </c>
       <c r="E63" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -15082,7 +15077,7 @@
         <v>49</v>
       </c>
       <c r="E64" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -15099,7 +15094,7 @@
         <v>71</v>
       </c>
       <c r="E65" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -15116,7 +15111,7 @@
         <v>64</v>
       </c>
       <c r="E66" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -15133,7 +15128,7 @@
         <v>49</v>
       </c>
       <c r="E67" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -15150,7 +15145,7 @@
         <v>64</v>
       </c>
       <c r="E68" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -15167,7 +15162,7 @@
         <v>64</v>
       </c>
       <c r="E69" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -15184,7 +15179,7 @@
         <v>57</v>
       </c>
       <c r="E70" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -15201,7 +15196,7 @@
         <v>54</v>
       </c>
       <c r="E71" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -15218,7 +15213,7 @@
         <v>54</v>
       </c>
       <c r="E72" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -15235,7 +15230,7 @@
         <v>54</v>
       </c>
       <c r="E73" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -15252,7 +15247,7 @@
         <v>66</v>
       </c>
       <c r="E74" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -15269,7 +15264,7 @@
         <v>69</v>
       </c>
       <c r="E75" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -15286,7 +15281,7 @@
         <v>65</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -15303,7 +15298,7 @@
         <v>65</v>
       </c>
       <c r="E77" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -15320,7 +15315,7 @@
         <v>53</v>
       </c>
       <c r="E78" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -15337,7 +15332,7 @@
         <v>65</v>
       </c>
       <c r="E79" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -15354,32 +15349,32 @@
         <v>54</v>
       </c>
       <c r="E80" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>267</v>
+      </c>
+      <c r="B81" t="s">
         <v>384</v>
       </c>
-      <c r="B81" t="s">
-        <v>385</v>
-      </c>
       <c r="C81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81">
-        <v>61</v>
-      </c>
-      <c r="E81" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="E81" s="35" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>385</v>
+      </c>
+      <c r="B82" t="s">
         <v>386</v>
-      </c>
-      <c r="B82" t="s">
-        <v>387</v>
       </c>
       <c r="C82">
         <v>25</v>
@@ -15388,15 +15383,15 @@
         <v>52</v>
       </c>
       <c r="E82" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>387</v>
+      </c>
+      <c r="B83" t="s">
         <v>388</v>
-      </c>
-      <c r="B83" t="s">
-        <v>389</v>
       </c>
       <c r="C83">
         <v>24</v>
@@ -15405,15 +15400,15 @@
         <v>53</v>
       </c>
       <c r="E83" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>389</v>
+      </c>
+      <c r="B84" t="s">
         <v>390</v>
-      </c>
-      <c r="B84" t="s">
-        <v>391</v>
       </c>
       <c r="C84">
         <v>26</v>
@@ -15422,15 +15417,15 @@
         <v>65</v>
       </c>
       <c r="E84" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>391</v>
+      </c>
+      <c r="B85" t="s">
         <v>392</v>
-      </c>
-      <c r="B85" t="s">
-        <v>393</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -15439,15 +15434,15 @@
         <v>0</v>
       </c>
       <c r="E85" s="35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>394</v>
+      </c>
+      <c r="B86" t="s">
         <v>395</v>
-      </c>
-      <c r="B86" t="s">
-        <v>396</v>
       </c>
       <c r="C86">
         <v>13</v>
@@ -15456,32 +15451,32 @@
         <v>80</v>
       </c>
       <c r="E86" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>396</v>
+      </c>
+      <c r="B87" t="s">
         <v>397</v>
-      </c>
-      <c r="B87" t="s">
-        <v>398</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E87" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>398</v>
+      </c>
+      <c r="B88" t="s">
         <v>399</v>
-      </c>
-      <c r="B88" t="s">
-        <v>400</v>
       </c>
       <c r="C88">
         <v>8</v>
@@ -15490,15 +15485,15 @@
         <v>53</v>
       </c>
       <c r="E88" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>400</v>
+      </c>
+      <c r="B89" t="s">
         <v>401</v>
-      </c>
-      <c r="B89" t="s">
-        <v>402</v>
       </c>
       <c r="C89">
         <v>8</v>
@@ -15507,15 +15502,15 @@
         <v>53</v>
       </c>
       <c r="E89" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>402</v>
+      </c>
+      <c r="B90" t="s">
         <v>403</v>
-      </c>
-      <c r="B90" t="s">
-        <v>404</v>
       </c>
       <c r="C90">
         <v>7</v>
@@ -15524,15 +15519,15 @@
         <v>52</v>
       </c>
       <c r="E90" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>404</v>
+      </c>
+      <c r="B91" t="s">
         <v>405</v>
-      </c>
-      <c r="B91" t="s">
-        <v>406</v>
       </c>
       <c r="C91">
         <v>13</v>
@@ -15541,7 +15536,7 @@
         <v>96</v>
       </c>
       <c r="E91" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -15549,7 +15544,7 @@
         <v>224</v>
       </c>
       <c r="B92" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C92">
         <v>27</v>
@@ -15558,7 +15553,7 @@
         <v>49</v>
       </c>
       <c r="E92" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -15566,7 +15561,7 @@
         <v>204</v>
       </c>
       <c r="B93" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C93">
         <v>7</v>
@@ -15575,15 +15570,15 @@
         <v>60</v>
       </c>
       <c r="E93" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>408</v>
+      </c>
+      <c r="B94" t="s">
         <v>409</v>
-      </c>
-      <c r="B94" t="s">
-        <v>410</v>
       </c>
       <c r="C94">
         <v>8</v>
@@ -15592,15 +15587,15 @@
         <v>57</v>
       </c>
       <c r="E94" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>410</v>
+      </c>
+      <c r="B95" t="s">
         <v>411</v>
-      </c>
-      <c r="B95" t="s">
-        <v>412</v>
       </c>
       <c r="C95">
         <v>8</v>
@@ -15609,15 +15604,15 @@
         <v>66</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>412</v>
+      </c>
+      <c r="B96" t="s">
         <v>413</v>
-      </c>
-      <c r="B96" t="s">
-        <v>414</v>
       </c>
       <c r="C96">
         <v>8</v>
@@ -15626,15 +15621,15 @@
         <v>61</v>
       </c>
       <c r="E96" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>414</v>
+      </c>
+      <c r="B97" t="s">
         <v>415</v>
-      </c>
-      <c r="B97" t="s">
-        <v>416</v>
       </c>
       <c r="C97">
         <v>7</v>
@@ -15643,15 +15638,15 @@
         <v>66</v>
       </c>
       <c r="E97" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>416</v>
+      </c>
+      <c r="B98" t="s">
         <v>417</v>
-      </c>
-      <c r="B98" t="s">
-        <v>418</v>
       </c>
       <c r="C98">
         <v>21</v>
@@ -15660,15 +15655,15 @@
         <v>79</v>
       </c>
       <c r="E98" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>418</v>
+      </c>
+      <c r="B99" t="s">
         <v>419</v>
-      </c>
-      <c r="B99" t="s">
-        <v>420</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -15677,15 +15672,15 @@
         <v>62</v>
       </c>
       <c r="E99" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" t="s">
         <v>421</v>
-      </c>
-      <c r="B100" t="s">
-        <v>422</v>
       </c>
       <c r="C100">
         <v>18</v>
@@ -15694,15 +15689,15 @@
         <v>65</v>
       </c>
       <c r="E100" s="32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>422</v>
+      </c>
+      <c r="B101" t="s">
         <v>423</v>
-      </c>
-      <c r="B101" t="s">
-        <v>424</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -15711,7 +15706,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -80,13 +80,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 00:11:04</t>
+    <t>02/09/2026, 00:36:22</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 45s</t>
+    <t>4m 39s</t>
   </si>
   <si>
     <t>Version</t>
@@ -137,7 +137,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5516 ms</t>
+    <t>5422 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -3258,7 +3258,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4977</v>
+        <v>4059</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -3329,7 +3329,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>4184</v>
+        <v>4003</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -3400,7 +3400,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5443</v>
+        <v>5870</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -3471,7 +3471,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5413</v>
+        <v>5362</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -3542,7 +3542,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5497</v>
+        <v>5682</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -3613,7 +3613,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4576</v>
+        <v>4664</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -3684,7 +3684,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>5095</v>
+        <v>4303</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -3755,7 +3755,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4389</v>
+        <v>4702</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -3826,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>5218</v>
+        <v>5212</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -3897,7 +3897,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>4845</v>
+        <v>5280</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -3968,7 +3968,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>4284</v>
+        <v>4719</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -4039,7 +4039,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>4893</v>
+        <v>4092</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -4110,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>6146</v>
+        <v>5277</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -4181,7 +4181,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>4806</v>
+        <v>4939</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -4252,7 +4252,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>4828</v>
+        <v>5978</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -4323,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>5263</v>
+        <v>4866</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -4394,7 +4394,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>5545</v>
+        <v>5417</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -4465,7 +4465,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>5338</v>
+        <v>5441</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>5939</v>
+        <v>4953</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -4607,7 +4607,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>4286</v>
+        <v>3836</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -4678,7 +4678,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>5003</v>
+        <v>5569</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -4749,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4653</v>
+        <v>4554</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -4820,7 +4820,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>5184</v>
+        <v>4854</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -4891,7 +4891,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4890</v>
+        <v>5357</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -4962,7 +4962,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>5358</v>
+        <v>5179</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -5033,7 +5033,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4796</v>
+        <v>4988</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -5104,7 +5104,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>4114</v>
+        <v>4653</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -5175,7 +5175,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4919</v>
+        <v>4242</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -5246,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>5341</v>
+        <v>5270</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -5317,7 +5317,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5399</v>
+        <v>4931</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -5388,7 +5388,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>6548</v>
+        <v>4343</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -5459,7 +5459,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>5924</v>
+        <v>5505</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5184</v>
+        <v>5367</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -5601,7 +5601,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5033</v>
+        <v>5118</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -5672,7 +5672,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4226</v>
+        <v>4056</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -5743,7 +5743,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5371</v>
+        <v>5277</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -5812,7 +5812,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30132</v>
+        <v>30120</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -5883,7 +5883,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>6727</v>
+        <v>5059</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -5954,7 +5954,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4380</v>
+        <v>4059</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -6025,7 +6025,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>4780</v>
+        <v>4685</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -6096,7 +6096,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>4776</v>
+        <v>4863</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -6167,7 +6167,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4108</v>
+        <v>4315</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -6238,7 +6238,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4239</v>
+        <v>4210</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -6309,7 +6309,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>4048</v>
+        <v>4839</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -6380,7 +6380,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>4702</v>
+        <v>4664</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -6451,7 +6451,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>3953</v>
+        <v>3996</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -6522,7 +6522,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>3912</v>
+        <v>6289</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -6593,7 +6593,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>5305</v>
+        <v>5162</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -6664,7 +6664,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5918</v>
+        <v>5876</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -6735,7 +6735,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5887</v>
+        <v>5035</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -80,13 +80,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 00:36:22</t>
+    <t>02/09/2026, 09:11:53</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 39s</t>
+    <t>4m 28s</t>
   </si>
   <si>
     <t>Version</t>
@@ -137,7 +137,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5422 ms</t>
+    <t>5192 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -3258,7 +3258,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4059</v>
+        <v>4452</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -3329,7 +3329,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>4003</v>
+        <v>3759</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -3400,7 +3400,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5870</v>
+        <v>5321</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -3471,7 +3471,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5362</v>
+        <v>5295</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -3542,7 +3542,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5682</v>
+        <v>4996</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -3613,7 +3613,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4664</v>
+        <v>5222</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -3684,7 +3684,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4303</v>
+        <v>4337</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -3755,7 +3755,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4702</v>
+        <v>4972</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -3826,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>5212</v>
+        <v>4178</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -3897,7 +3897,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>5280</v>
+        <v>4997</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -3968,7 +3968,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>4719</v>
+        <v>3885</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -4039,7 +4039,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>4092</v>
+        <v>3971</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -4110,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>5277</v>
+        <v>4965</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -4181,7 +4181,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>4939</v>
+        <v>3992</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -4252,7 +4252,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>5978</v>
+        <v>5182</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -4323,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>4866</v>
+        <v>4924</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -4394,7 +4394,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>5417</v>
+        <v>4973</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -4465,7 +4465,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>5441</v>
+        <v>5016</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>4953</v>
+        <v>6522</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -4607,7 +4607,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>3836</v>
+        <v>3672</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -4678,7 +4678,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>5569</v>
+        <v>4819</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -4749,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4554</v>
+        <v>5044</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -4820,7 +4820,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4854</v>
+        <v>4204</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -4891,7 +4891,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>5357</v>
+        <v>4622</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -4962,7 +4962,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>5179</v>
+        <v>5303</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -5033,7 +5033,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4988</v>
+        <v>4938</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -5104,7 +5104,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>4653</v>
+        <v>3738</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -5175,7 +5175,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4242</v>
+        <v>3916</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -5246,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>5270</v>
+        <v>4124</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -5317,7 +5317,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>4931</v>
+        <v>5227</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -5388,7 +5388,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4343</v>
+        <v>4266</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -5459,7 +5459,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>5505</v>
+        <v>7441</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5367</v>
+        <v>5502</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -5601,7 +5601,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5118</v>
+        <v>5268</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -5672,7 +5672,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4056</v>
+        <v>4000</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -5743,7 +5743,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5277</v>
+        <v>4484</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -5812,7 +5812,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30120</v>
+        <v>30113</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -5883,7 +5883,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5059</v>
+        <v>5302</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -5954,7 +5954,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4059</v>
+        <v>4882</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -6025,7 +6025,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>4685</v>
+        <v>3991</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -6096,7 +6096,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>4863</v>
+        <v>4455</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -6167,7 +6167,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4315</v>
+        <v>4739</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -6238,7 +6238,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4210</v>
+        <v>3949</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -6309,7 +6309,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>4839</v>
+        <v>3853</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -6380,7 +6380,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>4664</v>
+        <v>4084</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -6451,7 +6451,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>3996</v>
+        <v>3787</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -6522,7 +6522,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>6289</v>
+        <v>3835</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -6593,7 +6593,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>5162</v>
+        <v>4360</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -6664,7 +6664,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5876</v>
+        <v>5694</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -6735,7 +6735,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5035</v>
+        <v>5023</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -80,13 +80,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 09:11:53</t>
+    <t>02/09/2026, 10:00:58</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 28s</t>
+    <t>4m 33s</t>
   </si>
   <si>
     <t>Version</t>
@@ -137,7 +137,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5192 ms</t>
+    <t>5289 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -3231,7 +3231,7 @@
         <v>13</v>
       </c>
       <c r="K2" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L2" s="20">
         <v>59</v>
@@ -3258,7 +3258,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4452</v>
+        <v>4744</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -3302,7 +3302,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" s="20">
         <v>48</v>
@@ -3329,7 +3329,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>3759</v>
+        <v>3734</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -3373,7 +3373,7 @@
         <v>13</v>
       </c>
       <c r="K4" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L4" s="20">
         <v>75</v>
@@ -3400,7 +3400,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5321</v>
+        <v>4348</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -3444,7 +3444,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L5" s="20">
         <v>66</v>
@@ -3471,7 +3471,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5295</v>
+        <v>5320</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -3515,7 +3515,7 @@
         <v>13</v>
       </c>
       <c r="K6" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L6" s="20">
         <v>61</v>
@@ -3542,7 +3542,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>4996</v>
+        <v>4903</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -3586,7 +3586,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L7" s="20">
         <v>58</v>
@@ -3613,7 +3613,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>5222</v>
+        <v>4431</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -3657,7 +3657,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L8" s="20">
         <v>62</v>
@@ -3684,7 +3684,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4337</v>
+        <v>4874</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -3728,7 +3728,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L9" s="20">
         <v>56</v>
@@ -3755,7 +3755,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4972</v>
+        <v>4137</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -3799,7 +3799,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L10" s="20">
         <v>55</v>
@@ -3826,7 +3826,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4178</v>
+        <v>4192</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -3870,7 +3870,7 @@
         <v>13</v>
       </c>
       <c r="K11" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L11" s="20">
         <v>56</v>
@@ -3897,7 +3897,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>4997</v>
+        <v>4285</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -3941,7 +3941,7 @@
         <v>13</v>
       </c>
       <c r="K12" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L12" s="20">
         <v>70</v>
@@ -3968,7 +3968,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>3885</v>
+        <v>3800</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -4012,7 +4012,7 @@
         <v>13</v>
       </c>
       <c r="K13" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L13" s="20">
         <v>60</v>
@@ -4039,7 +4039,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>3971</v>
+        <v>3898</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -4083,7 +4083,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L14" s="20">
         <v>56</v>
@@ -4110,7 +4110,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>4965</v>
+        <v>5053</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -4154,7 +4154,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L15" s="20">
         <v>85</v>
@@ -4181,7 +4181,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>3992</v>
+        <v>4077</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -4225,7 +4225,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L16" s="20">
         <v>59</v>
@@ -4252,7 +4252,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>5182</v>
+        <v>5152</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -4296,7 +4296,7 @@
         <v>13</v>
       </c>
       <c r="K17" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L17" s="20">
         <v>57</v>
@@ -4323,7 +4323,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>4924</v>
+        <v>4767</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -4367,7 +4367,7 @@
         <v>13</v>
       </c>
       <c r="K18" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L18" s="20">
         <v>82</v>
@@ -4394,7 +4394,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>4973</v>
+        <v>5044</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -4438,7 +4438,7 @@
         <v>13</v>
       </c>
       <c r="K19" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L19" s="20">
         <v>63</v>
@@ -4465,7 +4465,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>5016</v>
+        <v>6319</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -4509,7 +4509,7 @@
         <v>13</v>
       </c>
       <c r="K20" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L20" s="20">
         <v>53</v>
@@ -4536,7 +4536,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>6522</v>
+        <v>5008</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -4580,7 +4580,7 @@
         <v>13</v>
       </c>
       <c r="K21" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L21" s="20">
         <v>48</v>
@@ -4607,7 +4607,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>3672</v>
+        <v>5295</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -4651,7 +4651,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L22" s="20">
         <v>51</v>
@@ -4678,7 +4678,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>4819</v>
+        <v>4227</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -4722,7 +4722,7 @@
         <v>13</v>
       </c>
       <c r="K23" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L23" s="20">
         <v>53</v>
@@ -4749,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>5044</v>
+        <v>4315</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -4793,7 +4793,7 @@
         <v>13</v>
       </c>
       <c r="K24" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L24" s="20">
         <v>75</v>
@@ -4820,7 +4820,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4204</v>
+        <v>4426</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -4864,7 +4864,7 @@
         <v>13</v>
       </c>
       <c r="K25" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L25" s="20">
         <v>60</v>
@@ -4891,7 +4891,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4622</v>
+        <v>4517</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -4935,7 +4935,7 @@
         <v>13</v>
       </c>
       <c r="K26" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L26" s="20">
         <v>60</v>
@@ -4962,7 +4962,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>5303</v>
+        <v>4651</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -5006,7 +5006,7 @@
         <v>13</v>
       </c>
       <c r="K27" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L27" s="20">
         <v>54</v>
@@ -5033,7 +5033,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4938</v>
+        <v>4433</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -5077,7 +5077,7 @@
         <v>13</v>
       </c>
       <c r="K28" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L28" s="20">
         <v>52</v>
@@ -5104,7 +5104,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>3738</v>
+        <v>6486</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -5148,7 +5148,7 @@
         <v>13</v>
       </c>
       <c r="K29" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L29" s="20">
         <v>59</v>
@@ -5175,7 +5175,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>3916</v>
+        <v>4514</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -5219,7 +5219,7 @@
         <v>13</v>
       </c>
       <c r="K30" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L30" s="20">
         <v>118</v>
@@ -5246,7 +5246,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>4124</v>
+        <v>4793</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -5290,7 +5290,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L31" s="20">
         <v>76</v>
@@ -5317,7 +5317,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5227</v>
+        <v>4360</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -5361,7 +5361,7 @@
         <v>13</v>
       </c>
       <c r="K32" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L32" s="20">
         <v>72</v>
@@ -5388,7 +5388,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4266</v>
+        <v>4287</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -5432,7 +5432,7 @@
         <v>13</v>
       </c>
       <c r="K33" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L33" s="20">
         <v>66</v>
@@ -5459,7 +5459,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>7441</v>
+        <v>5844</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -5503,7 +5503,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L34" s="20">
         <v>68</v>
@@ -5530,7 +5530,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5502</v>
+        <v>5046</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -5574,7 +5574,7 @@
         <v>13</v>
       </c>
       <c r="K35" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L35" s="20">
         <v>62</v>
@@ -5601,7 +5601,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5268</v>
+        <v>4914</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -5645,7 +5645,7 @@
         <v>13</v>
       </c>
       <c r="K36" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L36" s="20">
         <v>56</v>
@@ -5672,7 +5672,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4000</v>
+        <v>4270</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -5716,7 +5716,7 @@
         <v>13</v>
       </c>
       <c r="K37" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L37" s="20">
         <v>61</v>
@@ -5743,7 +5743,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>4484</v>
+        <v>4394</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -5812,7 +5812,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30113</v>
+        <v>30112</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -5856,7 +5856,7 @@
         <v>13</v>
       </c>
       <c r="K39" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L39" s="20">
         <v>61</v>
@@ -5883,7 +5883,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5302</v>
+        <v>5172</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -5927,7 +5927,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L40" s="20">
         <v>47</v>
@@ -5954,7 +5954,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4882</v>
+        <v>4501</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -5998,7 +5998,7 @@
         <v>13</v>
       </c>
       <c r="K41" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L41" s="20">
         <v>47</v>
@@ -6025,7 +6025,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>3991</v>
+        <v>9521</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -6069,7 +6069,7 @@
         <v>13</v>
       </c>
       <c r="K42" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L42" s="20">
         <v>47</v>
@@ -6096,7 +6096,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>4455</v>
+        <v>5438</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -6140,7 +6140,7 @@
         <v>13</v>
       </c>
       <c r="K43" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L43" s="20">
         <v>47</v>
@@ -6167,7 +6167,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4739</v>
+        <v>4255</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -6211,7 +6211,7 @@
         <v>13</v>
       </c>
       <c r="K44" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L44" s="20">
         <v>47</v>
@@ -6238,7 +6238,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>3949</v>
+        <v>4275</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -6282,7 +6282,7 @@
         <v>13</v>
       </c>
       <c r="K45" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L45" s="20">
         <v>57</v>
@@ -6309,7 +6309,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>3853</v>
+        <v>4196</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -6353,7 +6353,7 @@
         <v>13</v>
       </c>
       <c r="K46" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L46" s="20">
         <v>52</v>
@@ -6380,7 +6380,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>4084</v>
+        <v>3850</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -6424,7 +6424,7 @@
         <v>13</v>
       </c>
       <c r="K47" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L47" s="20">
         <v>47</v>
@@ -6451,7 +6451,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>3787</v>
+        <v>3915</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -6495,7 +6495,7 @@
         <v>13</v>
       </c>
       <c r="K48" s="20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L48" s="20">
         <v>47</v>
@@ -6522,7 +6522,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>3835</v>
+        <v>4945</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -6566,7 +6566,7 @@
         <v>13</v>
       </c>
       <c r="K49" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="20">
         <v>68</v>
@@ -6593,7 +6593,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>4360</v>
+        <v>4877</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -6637,7 +6637,7 @@
         <v>13</v>
       </c>
       <c r="K50" s="20">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L50" s="20">
         <v>68</v>
@@ -6664,7 +6664,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5694</v>
+        <v>5344</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -6708,7 +6708,7 @@
         <v>13</v>
       </c>
       <c r="K51" s="20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L51" s="20">
         <v>70</v>
@@ -6735,7 +6735,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5023</v>
+        <v>5186</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>
@@ -7875,7 +7875,7 @@
         <v>113</v>
       </c>
       <c r="C2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2">
         <v>59</v>
@@ -7892,7 +7892,7 @@
         <v>125</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>48</v>
@@ -7909,7 +7909,7 @@
         <v>132</v>
       </c>
       <c r="C4">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <v>75</v>
@@ -7926,7 +7926,7 @@
         <v>138</v>
       </c>
       <c r="C5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>66</v>
@@ -7943,7 +7943,7 @@
         <v>142</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6">
         <v>61</v>
@@ -7960,7 +7960,7 @@
         <v>144</v>
       </c>
       <c r="C7">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7">
         <v>58</v>
@@ -7977,7 +7977,7 @@
         <v>147</v>
       </c>
       <c r="C8">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>62</v>
@@ -7994,7 +7994,7 @@
         <v>150</v>
       </c>
       <c r="C9">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9">
         <v>56</v>
@@ -8011,7 +8011,7 @@
         <v>153</v>
       </c>
       <c r="C10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10">
         <v>55</v>
@@ -8028,7 +8028,7 @@
         <v>155</v>
       </c>
       <c r="C11">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11">
         <v>56</v>
@@ -8045,7 +8045,7 @@
         <v>157</v>
       </c>
       <c r="C12">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12">
         <v>70</v>
@@ -8062,7 +8062,7 @@
         <v>162</v>
       </c>
       <c r="C13">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13">
         <v>60</v>
@@ -8079,7 +8079,7 @@
         <v>164</v>
       </c>
       <c r="C14">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14">
         <v>56</v>
@@ -8096,7 +8096,7 @@
         <v>166</v>
       </c>
       <c r="C15">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15">
         <v>85</v>
@@ -8113,7 +8113,7 @@
         <v>170</v>
       </c>
       <c r="C16">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16">
         <v>59</v>
@@ -8130,7 +8130,7 @@
         <v>172</v>
       </c>
       <c r="C17">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17">
         <v>57</v>
@@ -8147,7 +8147,7 @@
         <v>139</v>
       </c>
       <c r="C18">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18">
         <v>82</v>
@@ -8164,7 +8164,7 @@
         <v>176</v>
       </c>
       <c r="C19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19">
         <v>63</v>
@@ -8181,7 +8181,7 @@
         <v>178</v>
       </c>
       <c r="C20">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20">
         <v>53</v>
@@ -8198,7 +8198,7 @@
         <v>180</v>
       </c>
       <c r="C21">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21">
         <v>48</v>
@@ -8215,7 +8215,7 @@
         <v>184</v>
       </c>
       <c r="C22">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D22">
         <v>51</v>
@@ -8232,7 +8232,7 @@
         <v>186</v>
       </c>
       <c r="C23">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
         <v>53</v>
@@ -8249,7 +8249,7 @@
         <v>188</v>
       </c>
       <c r="C24">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D24">
         <v>75</v>
@@ -8266,7 +8266,7 @@
         <v>190</v>
       </c>
       <c r="C25">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25">
         <v>60</v>
@@ -8283,7 +8283,7 @@
         <v>192</v>
       </c>
       <c r="C26">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D26">
         <v>60</v>
@@ -8300,7 +8300,7 @@
         <v>194</v>
       </c>
       <c r="C27">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27">
         <v>54</v>
@@ -8317,7 +8317,7 @@
         <v>196</v>
       </c>
       <c r="C28">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28">
         <v>52</v>
@@ -8334,7 +8334,7 @@
         <v>198</v>
       </c>
       <c r="C29">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29">
         <v>59</v>
@@ -8351,7 +8351,7 @@
         <v>202</v>
       </c>
       <c r="C30">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30">
         <v>118</v>
@@ -8368,7 +8368,7 @@
         <v>204</v>
       </c>
       <c r="C31">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D31">
         <v>76</v>
@@ -8385,7 +8385,7 @@
         <v>145</v>
       </c>
       <c r="C32">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D32">
         <v>72</v>
@@ -8402,7 +8402,7 @@
         <v>208</v>
       </c>
       <c r="C33">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33">
         <v>66</v>
@@ -8419,7 +8419,7 @@
         <v>210</v>
       </c>
       <c r="C34">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34">
         <v>68</v>
@@ -8436,7 +8436,7 @@
         <v>212</v>
       </c>
       <c r="C35">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D35">
         <v>62</v>
@@ -8453,7 +8453,7 @@
         <v>214</v>
       </c>
       <c r="C36">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D36">
         <v>56</v>
@@ -8470,7 +8470,7 @@
         <v>216</v>
       </c>
       <c r="C37">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37">
         <v>61</v>
@@ -8504,7 +8504,7 @@
         <v>220</v>
       </c>
       <c r="C39">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D39">
         <v>61</v>
@@ -8521,7 +8521,7 @@
         <v>222</v>
       </c>
       <c r="C40">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D40">
         <v>47</v>
@@ -8538,7 +8538,7 @@
         <v>227</v>
       </c>
       <c r="C41">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>47</v>
@@ -8555,7 +8555,7 @@
         <v>231</v>
       </c>
       <c r="C42">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42">
         <v>47</v>
@@ -8572,7 +8572,7 @@
         <v>236</v>
       </c>
       <c r="C43">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D43">
         <v>47</v>
@@ -8589,7 +8589,7 @@
         <v>240</v>
       </c>
       <c r="C44">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D44">
         <v>47</v>
@@ -8606,7 +8606,7 @@
         <v>244</v>
       </c>
       <c r="C45">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45">
         <v>57</v>
@@ -8623,7 +8623,7 @@
         <v>251</v>
       </c>
       <c r="C46">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D46">
         <v>52</v>
@@ -8640,7 +8640,7 @@
         <v>256</v>
       </c>
       <c r="C47">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47">
         <v>47</v>
@@ -8657,7 +8657,7 @@
         <v>261</v>
       </c>
       <c r="C48">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48">
         <v>47</v>
@@ -8674,7 +8674,7 @@
         <v>268</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>68</v>
@@ -8691,7 +8691,7 @@
         <v>273</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50">
         <v>68</v>
@@ -8708,7 +8708,7 @@
         <v>275</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51">
         <v>70</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -17,13 +17,15 @@
     <sheet sheetId="8" name="Orphan Pages" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Internal Links" state="visible" r:id="rId12"/>
     <sheet sheetId="10" name="Media Inventory" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Website Composition" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Most Referenced" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="326">
   <si>
     <t>ClubHub Insight</t>
   </si>
@@ -80,13 +82,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 10:00:58</t>
+    <t>02/09/2026, 11:25:31</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 33s</t>
+    <t>4m 45s</t>
   </si>
   <si>
     <t>Version</t>
@@ -137,7 +139,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5289 ms</t>
+    <t>5526 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -888,6 +890,120 @@
   </si>
   <si>
     <t>No Media</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Pages / Count</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Total Pages</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>Content Type Distribution</t>
+  </si>
+  <si>
+    <t>2%</t>
+  </si>
+  <si>
+    <t>28%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>ClubHub Areas</t>
+  </si>
+  <si>
+    <t>ClubHub Area</t>
+  </si>
+  <si>
+    <t>Health and Safety</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Governance</t>
+  </si>
+  <si>
+    <t>Club Development</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>People Development</t>
+  </si>
+  <si>
+    <t>Welfare and Safe Sport</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>Policies and Procedures</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>Video on Demand</t>
+  </si>
+  <si>
+    <t>Site Depth Distribution</t>
+  </si>
+  <si>
+    <t>Site Depth</t>
+  </si>
+  <si>
+    <t>Depth 0</t>
+  </si>
+  <si>
+    <t>Depth 1</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>Depth 2</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Media Composition</t>
+  </si>
+  <si>
+    <t>Link Composition</t>
+  </si>
+  <si>
+    <t>Internal Links</t>
+  </si>
+  <si>
+    <t>External Links</t>
+  </si>
+  <si>
+    <t>Rank</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1114,6 +1230,15 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2583,6 +2708,923 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:4" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="20">
+        <v>50</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="20">
+        <v>1</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="20">
+        <v>14</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="20">
+        <v>5</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="20">
+        <v>7</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="20">
+        <v>7</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" s="20">
+        <v>12</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="20">
+        <v>1</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="20">
+        <v>2</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="20">
+        <v>1</v>
+      </c>
+      <c r="D13" s="37" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="20">
+        <v>3</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B17" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" s="20">
+        <v>2</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>302</v>
+      </c>
+      <c r="B18" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" s="20">
+        <v>4</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>302</v>
+      </c>
+      <c r="B19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="20">
+        <v>3</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C20" s="20">
+        <v>0</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C21" s="20">
+        <v>6</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22" s="20">
+        <v>0</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C25" s="20">
+        <v>1</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>315</v>
+      </c>
+      <c r="B26" t="s">
+        <v>317</v>
+      </c>
+      <c r="C26" s="20">
+        <v>31</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" s="20">
+        <v>18</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>321</v>
+      </c>
+      <c r="B29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C29" s="20">
+        <v>1426</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="20">
+        <v>52</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B32" t="s">
+        <v>323</v>
+      </c>
+      <c r="C32" s="20">
+        <v>2977</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>322</v>
+      </c>
+      <c r="B33" t="s">
+        <v>324</v>
+      </c>
+      <c r="C33" s="20">
+        <v>706</v>
+      </c>
+      <c r="D33" s="37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="20" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="20">
+        <v>48</v>
+      </c>
+      <c r="F2" s="20">
+        <v>59</v>
+      </c>
+      <c r="G2" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="20">
+        <v>48</v>
+      </c>
+      <c r="F3" s="20">
+        <v>75</v>
+      </c>
+      <c r="G3" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="20">
+        <v>48</v>
+      </c>
+      <c r="F4" s="20">
+        <v>66</v>
+      </c>
+      <c r="G4" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="20">
+        <v>48</v>
+      </c>
+      <c r="F5" s="20">
+        <v>61</v>
+      </c>
+      <c r="G5" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="20">
+        <v>48</v>
+      </c>
+      <c r="F6" s="20">
+        <v>58</v>
+      </c>
+      <c r="G6" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="20">
+        <v>48</v>
+      </c>
+      <c r="F7" s="20">
+        <v>62</v>
+      </c>
+      <c r="G7" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E8" s="20">
+        <v>48</v>
+      </c>
+      <c r="F8" s="20">
+        <v>56</v>
+      </c>
+      <c r="G8" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="20">
+        <v>48</v>
+      </c>
+      <c r="F9" s="20">
+        <v>55</v>
+      </c>
+      <c r="G9" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="20">
+        <v>48</v>
+      </c>
+      <c r="F10" s="20">
+        <v>56</v>
+      </c>
+      <c r="G10" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" s="20">
+        <v>48</v>
+      </c>
+      <c r="F11" s="20">
+        <v>70</v>
+      </c>
+      <c r="G11" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E12" s="20">
+        <v>48</v>
+      </c>
+      <c r="F12" s="20">
+        <v>60</v>
+      </c>
+      <c r="G12" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="20">
+        <v>48</v>
+      </c>
+      <c r="F13" s="20">
+        <v>56</v>
+      </c>
+      <c r="G13" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="20">
+        <v>48</v>
+      </c>
+      <c r="F14" s="20">
+        <v>85</v>
+      </c>
+      <c r="G14" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="20">
+        <v>48</v>
+      </c>
+      <c r="F15" s="20">
+        <v>59</v>
+      </c>
+      <c r="G15" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="20">
+        <v>48</v>
+      </c>
+      <c r="F16" s="20">
+        <v>57</v>
+      </c>
+      <c r="G16" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="20">
+        <v>48</v>
+      </c>
+      <c r="F17" s="20">
+        <v>82</v>
+      </c>
+      <c r="G17" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="20">
+        <v>48</v>
+      </c>
+      <c r="F18" s="20">
+        <v>63</v>
+      </c>
+      <c r="G18" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="20">
+        <v>48</v>
+      </c>
+      <c r="F19" s="20">
+        <v>53</v>
+      </c>
+      <c r="G19" s="39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" t="s">
+        <v>181</v>
+      </c>
+      <c r="E20" s="20">
+        <v>48</v>
+      </c>
+      <c r="F20" s="20">
+        <v>48</v>
+      </c>
+      <c r="G20" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="20">
+        <v>48</v>
+      </c>
+      <c r="F21" s="20">
+        <v>51</v>
+      </c>
+      <c r="G21" s="39">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -3258,7 +4300,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4744</v>
+        <v>4910</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -3329,7 +4371,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>3734</v>
+        <v>4559</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -3400,7 +4442,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>4348</v>
+        <v>5475</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -3471,7 +4513,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5320</v>
+        <v>5483</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -3542,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>4903</v>
+        <v>5020</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -3613,7 +4655,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4431</v>
+        <v>4534</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -3684,7 +4726,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4874</v>
+        <v>4418</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -3755,7 +4797,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4137</v>
+        <v>5392</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -3826,7 +4868,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4192</v>
+        <v>4989</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -3897,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>4285</v>
+        <v>5170</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -3968,7 +5010,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>3800</v>
+        <v>4772</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -4039,7 +5081,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>3898</v>
+        <v>4146</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -4110,7 +5152,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>5053</v>
+        <v>4900</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -4181,7 +5223,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>4077</v>
+        <v>5262</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -4252,7 +5294,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>5152</v>
+        <v>6788</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -4323,7 +5365,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>4767</v>
+        <v>5116</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -4394,7 +5436,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>5044</v>
+        <v>5254</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -4465,7 +5507,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>6319</v>
+        <v>5422</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -4536,7 +5578,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>5008</v>
+        <v>7407</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -4607,7 +5649,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>5295</v>
+        <v>3946</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -4678,7 +5720,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>4227</v>
+        <v>6183</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -4749,7 +5791,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4315</v>
+        <v>4485</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -4820,7 +5862,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4426</v>
+        <v>4571</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -4891,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4517</v>
+        <v>4754</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -4962,7 +6004,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>4651</v>
+        <v>6221</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -5033,7 +6075,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4433</v>
+        <v>4668</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -5104,7 +6146,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>6486</v>
+        <v>4658</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -5175,7 +6217,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4514</v>
+        <v>4114</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -5246,7 +6288,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>4793</v>
+        <v>4646</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -5317,7 +6359,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>4360</v>
+        <v>5480</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -5388,7 +6430,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4287</v>
+        <v>4758</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -5459,7 +6501,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>5844</v>
+        <v>5252</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -5530,7 +6572,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5046</v>
+        <v>5485</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -5601,7 +6643,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>4914</v>
+        <v>5145</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -5672,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4270</v>
+        <v>4154</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -5743,7 +6785,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>4394</v>
+        <v>5074</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -5812,7 +6854,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30112</v>
+        <v>30115</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -5883,7 +6925,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5172</v>
+        <v>5257</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -5954,7 +6996,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4501</v>
+        <v>4272</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -6025,7 +7067,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>9521</v>
+        <v>4817</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -6096,7 +7138,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>5438</v>
+        <v>5407</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -6167,7 +7209,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4255</v>
+        <v>4570</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -6238,7 +7280,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4275</v>
+        <v>4955</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -6309,7 +7351,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>4196</v>
+        <v>4171</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -6380,7 +7422,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>3850</v>
+        <v>6170</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -6451,7 +7493,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>3915</v>
+        <v>4533</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -6522,7 +7564,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>4945</v>
+        <v>3989</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -6593,7 +7635,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>4877</v>
+        <v>5028</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -6664,7 +7706,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5344</v>
+        <v>5219</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -6735,7 +7777,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5186</v>
+        <v>5199</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -82,13 +82,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 11:25:31</t>
+    <t>02/09/2026, 12:15:42</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 45s</t>
+    <t>4m 58s</t>
   </si>
   <si>
     <t>Version</t>
@@ -139,7 +139,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5526 ms</t>
+    <t>5787 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -3094,7 +3094,7 @@
         <v>323</v>
       </c>
       <c r="C32" s="20">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="D32" s="37" t="s">
         <v>13</v>
@@ -3833,7 +3833,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="12">
-        <v>2977</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4910</v>
+        <v>5183</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -4371,7 +4371,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>4559</v>
+        <v>4980</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -4442,7 +4442,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5475</v>
+        <v>5010</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -4513,7 +4513,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5483</v>
+        <v>5358</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -4584,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5020</v>
+        <v>5058</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -4655,7 +4655,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4534</v>
+        <v>4823</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -4726,7 +4726,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4418</v>
+        <v>6115</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -4797,7 +4797,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>5392</v>
+        <v>4484</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -4868,7 +4868,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4989</v>
+        <v>4992</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -4939,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>5170</v>
+        <v>4761</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -5010,7 +5010,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>4772</v>
+        <v>4269</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -5081,7 +5081,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>4146</v>
+        <v>4093</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -5152,7 +5152,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>4900</v>
+        <v>5053</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -5223,7 +5223,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>5262</v>
+        <v>5367</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -5294,7 +5294,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>6788</v>
+        <v>5619</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -5365,7 +5365,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>5116</v>
+        <v>4723</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -5436,7 +5436,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>5254</v>
+        <v>5272</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -5507,7 +5507,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>5422</v>
+        <v>4750</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -5578,7 +5578,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>7407</v>
+        <v>5192</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -5649,7 +5649,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>3946</v>
+        <v>4059</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -5720,7 +5720,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>6183</v>
+        <v>5006</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -5791,7 +5791,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4485</v>
+        <v>5047</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -5862,7 +5862,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4571</v>
+        <v>4737</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -5933,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4754</v>
+        <v>5268</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -6004,7 +6004,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>6221</v>
+        <v>4736</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -6075,7 +6075,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4668</v>
+        <v>6288</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -6146,7 +6146,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>4658</v>
+        <v>5312</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -6217,7 +6217,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4114</v>
+        <v>4676</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -6288,7 +6288,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>4646</v>
+        <v>5026</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -6359,7 +6359,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5480</v>
+        <v>5767</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -6430,7 +6430,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4758</v>
+        <v>4765</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -6501,7 +6501,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>5252</v>
+        <v>6760</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -6572,7 +6572,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5485</v>
+        <v>5188</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -6643,7 +6643,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5145</v>
+        <v>5036</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -6714,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4154</v>
+        <v>4245</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -6785,7 +6785,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5074</v>
+        <v>5210</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -6854,7 +6854,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30115</v>
+        <v>30120</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -6925,7 +6925,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5257</v>
+        <v>5780</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -6996,7 +6996,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4272</v>
+        <v>4289</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -7067,7 +7067,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>4817</v>
+        <v>4815</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -7138,7 +7138,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>5407</v>
+        <v>5047</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -7209,7 +7209,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4570</v>
+        <v>4630</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -7280,7 +7280,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4955</v>
+        <v>4343</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -7351,7 +7351,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>4171</v>
+        <v>3993</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -7422,7 +7422,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>6170</v>
+        <v>7378</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -7493,7 +7493,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>4533</v>
+        <v>4531</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -7564,7 +7564,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>3989</v>
+        <v>4468</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -7635,7 +7635,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>5028</v>
+        <v>4643</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -7706,7 +7706,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5219</v>
+        <v>5170</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="20">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M51" s="21">
         <v>36</v>
@@ -7777,7 +7777,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5199</v>
+        <v>17909</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>
@@ -9753,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E51" s="32" t="s">
         <v>282</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -82,13 +82,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 12:15:42</t>
+    <t>02/09/2026, 12:58:34</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 58s</t>
+    <t>4m 51s</t>
   </si>
   <si>
     <t>Version</t>
@@ -139,7 +139,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5787 ms</t>
+    <t>5660 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -3094,7 +3094,7 @@
         <v>323</v>
       </c>
       <c r="C32" s="20">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="D32" s="37" t="s">
         <v>13</v>
@@ -3833,7 +3833,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="12">
-        <v>2978</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4300,7 +4300,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>5183</v>
+        <v>4954</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -4371,7 +4371,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>4980</v>
+        <v>3815</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -4442,7 +4442,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>5010</v>
+        <v>6357</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -4513,7 +4513,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5358</v>
+        <v>5777</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -4584,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5058</v>
+        <v>5061</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -4655,7 +4655,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4823</v>
+        <v>4731</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -4726,7 +4726,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>6115</v>
+        <v>4657</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -4797,7 +4797,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4484</v>
+        <v>4603</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -4868,7 +4868,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4992</v>
+        <v>4920</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -4939,7 +4939,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>4761</v>
+        <v>5172</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -5010,7 +5010,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>4269</v>
+        <v>4829</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -5081,7 +5081,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>4093</v>
+        <v>4895</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -5152,7 +5152,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>5053</v>
+        <v>5336</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -5223,7 +5223,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>5367</v>
+        <v>5861</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -5294,7 +5294,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>5619</v>
+        <v>10765</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -5365,7 +5365,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>4723</v>
+        <v>5244</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -5436,7 +5436,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>5272</v>
+        <v>7146</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -5507,7 +5507,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>4750</v>
+        <v>4981</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -5578,7 +5578,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>5192</v>
+        <v>4652</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -5649,7 +5649,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>4059</v>
+        <v>3297</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -5720,7 +5720,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>5006</v>
+        <v>5007</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -5791,7 +5791,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>5047</v>
+        <v>4936</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -5862,7 +5862,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4737</v>
+        <v>4925</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -5933,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>5268</v>
+        <v>4969</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -6004,7 +6004,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>4736</v>
+        <v>5284</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -6075,7 +6075,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>6288</v>
+        <v>4558</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -6146,7 +6146,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>5312</v>
+        <v>4013</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -6217,7 +6217,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4676</v>
+        <v>4225</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -6288,7 +6288,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>5026</v>
+        <v>4971</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -6359,7 +6359,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5767</v>
+        <v>5180</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -6430,7 +6430,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4765</v>
+        <v>4384</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -6501,7 +6501,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>6760</v>
+        <v>9626</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -6572,7 +6572,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>5188</v>
+        <v>7176</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -6643,7 +6643,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5036</v>
+        <v>5403</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -6714,7 +6714,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4245</v>
+        <v>4067</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -6785,7 +6785,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5210</v>
+        <v>5979</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -6854,7 +6854,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30120</v>
+        <v>30130</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -6925,7 +6925,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5780</v>
+        <v>5241</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -6996,7 +6996,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4289</v>
+        <v>4224</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -7067,7 +7067,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>4815</v>
+        <v>4864</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -7138,7 +7138,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>5047</v>
+        <v>5642</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -7209,7 +7209,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>4630</v>
+        <v>3946</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -7280,7 +7280,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4343</v>
+        <v>4104</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -7351,7 +7351,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>3993</v>
+        <v>4143</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -7422,7 +7422,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>7378</v>
+        <v>4120</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -7493,7 +7493,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>4531</v>
+        <v>4776</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -7564,7 +7564,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>4468</v>
+        <v>4201</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -7635,7 +7635,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>4643</v>
+        <v>4708</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -7706,7 +7706,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5170</v>
+        <v>5315</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="20">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M51" s="21">
         <v>36</v>
@@ -7777,7 +7777,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>17909</v>
+        <v>5849</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>
@@ -9753,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E51" s="32" t="s">
         <v>282</v>

--- a/output/ClubHubInsight.xlsx
+++ b/output/ClubHubInsight.xlsx
@@ -19,13 +19,14 @@
     <sheet sheetId="10" name="Media Inventory" state="visible" r:id="rId13"/>
     <sheet sheetId="11" name="Website Composition" state="visible" r:id="rId14"/>
     <sheet sheetId="12" name="Most Referenced" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Largest Pages" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="328">
   <si>
     <t>ClubHub Insight</t>
   </si>
@@ -82,13 +83,13 @@
     <t>Crawl Date</t>
   </si>
   <si>
-    <t>02/09/2026, 12:58:34</t>
+    <t>02/09/2026, 16:13:02</t>
   </si>
   <si>
     <t>Crawl Duration</t>
   </si>
   <si>
-    <t>4m 51s</t>
+    <t>5m 2s</t>
   </si>
   <si>
     <t>Version</t>
@@ -139,7 +140,7 @@
     <t>Average Page Load (ms)</t>
   </si>
   <si>
-    <t>5660 ms</t>
+    <t>5850 ms</t>
   </si>
   <si>
     <t>Site Structure</t>
@@ -1004,6 +1005,12 @@
   </si>
   <si>
     <t>Rank</t>
+  </si>
+  <si>
+    <t>HTML Size (Bytes)</t>
+  </si>
+  <si>
+    <t>HTML Size (KB)</t>
   </si>
 </sst>
 </file>
@@ -3625,6 +3632,572 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="65" customWidth="1"/>
+    <col min="3" max="3" width="75" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="8" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2">
+        <v>525642</v>
+      </c>
+      <c r="F2">
+        <v>513.3</v>
+      </c>
+      <c r="G2">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3">
+        <v>487051</v>
+      </c>
+      <c r="F3">
+        <v>475.6</v>
+      </c>
+      <c r="G3">
+        <v>34</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>484186</v>
+      </c>
+      <c r="F4">
+        <v>472.8</v>
+      </c>
+      <c r="G4">
+        <v>34</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5">
+        <v>483350</v>
+      </c>
+      <c r="F5">
+        <v>472</v>
+      </c>
+      <c r="G5">
+        <v>35</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6">
+        <v>482920</v>
+      </c>
+      <c r="F6">
+        <v>471.6</v>
+      </c>
+      <c r="G6">
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7">
+        <v>481949</v>
+      </c>
+      <c r="F7">
+        <v>470.7</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E8">
+        <v>481315</v>
+      </c>
+      <c r="F8">
+        <v>470</v>
+      </c>
+      <c r="G8">
+        <v>37</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9">
+        <v>480751</v>
+      </c>
+      <c r="F9">
+        <v>469.5</v>
+      </c>
+      <c r="G9">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" t="s">
+        <v>273</v>
+      </c>
+      <c r="D10" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10">
+        <v>477622</v>
+      </c>
+      <c r="F10">
+        <v>466.4</v>
+      </c>
+      <c r="G10">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E11">
+        <v>476699</v>
+      </c>
+      <c r="F11">
+        <v>465.5</v>
+      </c>
+      <c r="G11">
+        <v>29</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12">
+        <v>461677</v>
+      </c>
+      <c r="F12">
+        <v>450.9</v>
+      </c>
+      <c r="G12">
+        <v>31</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13">
+        <v>454631</v>
+      </c>
+      <c r="F13">
+        <v>444</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C14" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14">
+        <v>439113</v>
+      </c>
+      <c r="F14">
+        <v>428.8</v>
+      </c>
+      <c r="G14">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15">
+        <v>437559</v>
+      </c>
+      <c r="F15">
+        <v>427.3</v>
+      </c>
+      <c r="G15">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" t="s">
+        <v>190</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16">
+        <v>436130</v>
+      </c>
+      <c r="F16">
+        <v>425.9</v>
+      </c>
+      <c r="G16">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17">
+        <v>435243</v>
+      </c>
+      <c r="F17">
+        <v>425</v>
+      </c>
+      <c r="G17">
+        <v>30</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" t="s">
+        <v>170</v>
+      </c>
+      <c r="D18" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18">
+        <v>432173</v>
+      </c>
+      <c r="F18">
+        <v>422</v>
+      </c>
+      <c r="G18">
+        <v>34</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E19">
+        <v>431210</v>
+      </c>
+      <c r="F19">
+        <v>421.1</v>
+      </c>
+      <c r="G19">
+        <v>29</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>211</v>
+      </c>
+      <c r="C20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20">
+        <v>430548</v>
+      </c>
+      <c r="F20">
+        <v>420.5</v>
+      </c>
+      <c r="G20">
+        <v>29</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E21">
+        <v>415804</v>
+      </c>
+      <c r="F21">
+        <v>406.1</v>
+      </c>
+      <c r="G21">
+        <v>25</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
@@ -4300,7 +4873,7 @@
         <v>121</v>
       </c>
       <c r="T2" s="22">
-        <v>4954</v>
+        <v>4811</v>
       </c>
       <c r="U2" s="19" t="s">
         <v>122</v>
@@ -4371,7 +4944,7 @@
         <v>130</v>
       </c>
       <c r="T3" s="22">
-        <v>3815</v>
+        <v>4820</v>
       </c>
       <c r="U3" s="19" t="s">
         <v>122</v>
@@ -4442,7 +5015,7 @@
         <v>13</v>
       </c>
       <c r="T4" s="22">
-        <v>6357</v>
+        <v>5798</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>135</v>
@@ -4513,7 +5086,7 @@
         <v>13</v>
       </c>
       <c r="T5" s="22">
-        <v>5777</v>
+        <v>6191</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>135</v>
@@ -4584,7 +5157,7 @@
         <v>13</v>
       </c>
       <c r="T6" s="22">
-        <v>5061</v>
+        <v>5919</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>135</v>
@@ -4655,7 +5228,7 @@
         <v>13</v>
       </c>
       <c r="T7" s="22">
-        <v>4731</v>
+        <v>5114</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>135</v>
@@ -4726,7 +5299,7 @@
         <v>13</v>
       </c>
       <c r="T8" s="22">
-        <v>4657</v>
+        <v>5129</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>135</v>
@@ -4797,7 +5370,7 @@
         <v>13</v>
       </c>
       <c r="T9" s="22">
-        <v>4603</v>
+        <v>4842</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>135</v>
@@ -4868,7 +5441,7 @@
         <v>13</v>
       </c>
       <c r="T10" s="22">
-        <v>4920</v>
+        <v>4700</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>135</v>
@@ -4939,7 +5512,7 @@
         <v>13</v>
       </c>
       <c r="T11" s="22">
-        <v>5172</v>
+        <v>6629</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>135</v>
@@ -5010,7 +5583,7 @@
         <v>160</v>
       </c>
       <c r="T12" s="22">
-        <v>4829</v>
+        <v>4921</v>
       </c>
       <c r="U12" s="19" t="s">
         <v>122</v>
@@ -5081,7 +5654,7 @@
         <v>13</v>
       </c>
       <c r="T13" s="22">
-        <v>4895</v>
+        <v>4338</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>135</v>
@@ -5152,7 +5725,7 @@
         <v>13</v>
       </c>
       <c r="T14" s="22">
-        <v>5336</v>
+        <v>5363</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>135</v>
@@ -5223,7 +5796,7 @@
         <v>168</v>
       </c>
       <c r="T15" s="22">
-        <v>5861</v>
+        <v>5259</v>
       </c>
       <c r="U15" s="19" t="s">
         <v>122</v>
@@ -5294,7 +5867,7 @@
         <v>13</v>
       </c>
       <c r="T16" s="22">
-        <v>10765</v>
+        <v>5116</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>135</v>
@@ -5365,7 +5938,7 @@
         <v>13</v>
       </c>
       <c r="T17" s="22">
-        <v>5244</v>
+        <v>4628</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>135</v>
@@ -5436,7 +6009,7 @@
         <v>13</v>
       </c>
       <c r="T18" s="22">
-        <v>7146</v>
+        <v>6062</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>135</v>
@@ -5507,7 +6080,7 @@
         <v>13</v>
       </c>
       <c r="T19" s="22">
-        <v>4981</v>
+        <v>5377</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>135</v>
@@ -5578,7 +6151,7 @@
         <v>13</v>
       </c>
       <c r="T20" s="22">
-        <v>4652</v>
+        <v>4982</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>135</v>
@@ -5649,7 +6222,7 @@
         <v>13</v>
       </c>
       <c r="T21" s="22">
-        <v>3297</v>
+        <v>3504</v>
       </c>
       <c r="U21" s="25" t="s">
         <v>135</v>
@@ -5720,7 +6293,7 @@
         <v>13</v>
       </c>
       <c r="T22" s="22">
-        <v>5007</v>
+        <v>5204</v>
       </c>
       <c r="U22" s="25" t="s">
         <v>135</v>
@@ -5791,7 +6364,7 @@
         <v>13</v>
       </c>
       <c r="T23" s="22">
-        <v>4936</v>
+        <v>7001</v>
       </c>
       <c r="U23" s="25" t="s">
         <v>135</v>
@@ -5862,7 +6435,7 @@
         <v>13</v>
       </c>
       <c r="T24" s="22">
-        <v>4925</v>
+        <v>6399</v>
       </c>
       <c r="U24" s="25" t="s">
         <v>135</v>
@@ -5933,7 +6506,7 @@
         <v>13</v>
       </c>
       <c r="T25" s="22">
-        <v>4969</v>
+        <v>5758</v>
       </c>
       <c r="U25" s="25" t="s">
         <v>135</v>
@@ -6004,7 +6577,7 @@
         <v>13</v>
       </c>
       <c r="T26" s="22">
-        <v>5284</v>
+        <v>5741</v>
       </c>
       <c r="U26" s="25" t="s">
         <v>135</v>
@@ -6075,7 +6648,7 @@
         <v>13</v>
       </c>
       <c r="T27" s="22">
-        <v>4558</v>
+        <v>5093</v>
       </c>
       <c r="U27" s="25" t="s">
         <v>135</v>
@@ -6146,7 +6719,7 @@
         <v>13</v>
       </c>
       <c r="T28" s="22">
-        <v>4013</v>
+        <v>4945</v>
       </c>
       <c r="U28" s="25" t="s">
         <v>135</v>
@@ -6217,7 +6790,7 @@
         <v>200</v>
       </c>
       <c r="T29" s="22">
-        <v>4225</v>
+        <v>5421</v>
       </c>
       <c r="U29" s="19" t="s">
         <v>122</v>
@@ -6288,7 +6861,7 @@
         <v>13</v>
       </c>
       <c r="T30" s="22">
-        <v>4971</v>
+        <v>4838</v>
       </c>
       <c r="U30" s="25" t="s">
         <v>135</v>
@@ -6359,7 +6932,7 @@
         <v>13</v>
       </c>
       <c r="T31" s="22">
-        <v>5180</v>
+        <v>5610</v>
       </c>
       <c r="U31" s="25" t="s">
         <v>135</v>
@@ -6430,7 +7003,7 @@
         <v>13</v>
       </c>
       <c r="T32" s="22">
-        <v>4384</v>
+        <v>4746</v>
       </c>
       <c r="U32" s="25" t="s">
         <v>135</v>
@@ -6501,7 +7074,7 @@
         <v>13</v>
       </c>
       <c r="T33" s="22">
-        <v>9626</v>
+        <v>6125</v>
       </c>
       <c r="U33" s="25" t="s">
         <v>135</v>
@@ -6572,7 +7145,7 @@
         <v>13</v>
       </c>
       <c r="T34" s="22">
-        <v>7176</v>
+        <v>6220</v>
       </c>
       <c r="U34" s="25" t="s">
         <v>135</v>
@@ -6643,7 +7216,7 @@
         <v>13</v>
       </c>
       <c r="T35" s="22">
-        <v>5403</v>
+        <v>5228</v>
       </c>
       <c r="U35" s="25" t="s">
         <v>135</v>
@@ -6714,7 +7287,7 @@
         <v>13</v>
       </c>
       <c r="T36" s="22">
-        <v>4067</v>
+        <v>4264</v>
       </c>
       <c r="U36" s="25" t="s">
         <v>135</v>
@@ -6785,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="T37" s="22">
-        <v>5979</v>
+        <v>5772</v>
       </c>
       <c r="U37" s="25" t="s">
         <v>135</v>
@@ -6854,7 +7427,7 @@
         <v>13</v>
       </c>
       <c r="T38" s="22">
-        <v>30130</v>
+        <v>30116</v>
       </c>
       <c r="U38" s="25" t="s">
         <v>135</v>
@@ -6925,7 +7498,7 @@
         <v>13</v>
       </c>
       <c r="T39" s="22">
-        <v>5241</v>
+        <v>6106</v>
       </c>
       <c r="U39" s="25" t="s">
         <v>135</v>
@@ -6996,7 +7569,7 @@
         <v>225</v>
       </c>
       <c r="T40" s="22">
-        <v>4224</v>
+        <v>5846</v>
       </c>
       <c r="U40" s="19" t="s">
         <v>122</v>
@@ -7067,7 +7640,7 @@
         <v>229</v>
       </c>
       <c r="T41" s="22">
-        <v>4864</v>
+        <v>4952</v>
       </c>
       <c r="U41" s="19" t="s">
         <v>122</v>
@@ -7138,7 +7711,7 @@
         <v>234</v>
       </c>
       <c r="T42" s="22">
-        <v>5642</v>
+        <v>5397</v>
       </c>
       <c r="U42" s="19" t="s">
         <v>122</v>
@@ -7209,7 +7782,7 @@
         <v>238</v>
       </c>
       <c r="T43" s="22">
-        <v>3946</v>
+        <v>4615</v>
       </c>
       <c r="U43" s="19" t="s">
         <v>122</v>
@@ -7280,7 +7853,7 @@
         <v>242</v>
       </c>
       <c r="T44" s="22">
-        <v>4104</v>
+        <v>4894</v>
       </c>
       <c r="U44" s="19" t="s">
         <v>122</v>
@@ -7351,7 +7924,7 @@
         <v>249</v>
       </c>
       <c r="T45" s="22">
-        <v>4143</v>
+        <v>5923</v>
       </c>
       <c r="U45" s="19" t="s">
         <v>122</v>
@@ -7422,7 +7995,7 @@
         <v>254</v>
       </c>
       <c r="T46" s="22">
-        <v>4120</v>
+        <v>5203</v>
       </c>
       <c r="U46" s="19" t="s">
         <v>122</v>
@@ -7493,7 +8066,7 @@
         <v>259</v>
       </c>
       <c r="T47" s="22">
-        <v>4776</v>
+        <v>3981</v>
       </c>
       <c r="U47" s="19" t="s">
         <v>122</v>
@@ -7564,7 +8137,7 @@
         <v>266</v>
       </c>
       <c r="T48" s="22">
-        <v>4201</v>
+        <v>4814</v>
       </c>
       <c r="U48" s="19" t="s">
         <v>122</v>
@@ -7635,7 +8208,7 @@
         <v>271</v>
       </c>
       <c r="T49" s="22">
-        <v>4708</v>
+        <v>6621</v>
       </c>
       <c r="U49" s="19" t="s">
         <v>122</v>
@@ -7706,7 +8279,7 @@
         <v>13</v>
       </c>
       <c r="T50" s="22">
-        <v>5315</v>
+        <v>6468</v>
       </c>
       <c r="U50" s="25" t="s">
         <v>135</v>
@@ -7777,7 +8350,7 @@
         <v>13</v>
       </c>
       <c r="T51" s="22">
-        <v>5849</v>
+        <v>5719</v>
       </c>
       <c r="U51" s="25" t="s">
         <v>135</v>
